--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N739"/>
+  <dimension ref="A1:N736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PRC-29.012/2016-D</t>
+          <t>PRC-29.010/2010-D</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PRC-29.012/2016-D</t>
+          <t>PRC-29.010/2010-D</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PRC-22.018/2017-C</t>
+          <t>PRC-22.018/2011-C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PRC-22.038/2017-B</t>
+          <t>PRC-22.038/2012</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PRC-22.024/2018-A</t>
+          <t>PRC-22.024/2013</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PRC-24.010/2018-D</t>
+          <t>PRC-24.010/2013</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 4</t>
+          <t>PRC-22.090/2013-DO 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-B</t>
+          <t>PRC-22.013/2014</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9073557</t>
+          <t>PRC-29.012/2016-D</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9073557</t>
+          <t>PRC-29.012/2016-D</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DP-001/2023</t>
+          <t>DP-001/2022</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DC-021/2022</t>
+          <t>DC-021/2021</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP-003/2023</t>
+          <t>DP-003/2022</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP-003/2021</t>
+          <t>DP-002/2022</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PRC-22.015/2017-D</t>
+          <t>PRC-22.015/2017-C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PRC-22.015/2017-E</t>
+          <t>PRC-22.015/2017-D</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PRC-22.016/2018-B</t>
+          <t>PRC-22.015/2017-E</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PRC-22.020/2017-D</t>
+          <t>PRC-22.020/2017-C</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PRC-22.020/2017-E</t>
+          <t>PRC-22.020/2017-D</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PRC-22.022/2017-C</t>
+          <t>PRC-22.020/2017-E</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PRC-22.026/2017-C</t>
+          <t>PRC-22.026/2017-B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PRC-22.026/2017-D</t>
+          <t>PRC-22.026/2017-C</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PRC-22.026/2017-E</t>
+          <t>PRC-22.026/2017-D</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PRC-22.027/2017-B</t>
+          <t>PRC-22.026/2017-E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PRC-22.035/2017-C</t>
+          <t>PRC-22.035/2017-B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PRC-22.035/2017-D</t>
+          <t>PRC-22.035/2017-C</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PRC-22.035/2017-E</t>
+          <t>PRC-22.035/2017-D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PRC-22.037/2017-B</t>
+          <t>PRC-22.035/2017-E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PRC-22.029/2017-C</t>
+          <t>PRC-22.029/2017-B</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PRC-22.029/2017-D</t>
+          <t>PRC-22.029/2017-C</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PRC-22.029/2017-E</t>
+          <t>PRC-22.029/2017-D</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PRC-22.030/2017-B</t>
+          <t>PRC-22.029/2017-E</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PRC-22.043/2017-C</t>
+          <t>PRC-22.043/2017-B</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PRC-22.043/2017-D</t>
+          <t>PRC-22.043/2017-C</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PRC-22.043/2017-E</t>
+          <t>PRC-22.043/2017-D</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PRC-22.090/2013-DO 2</t>
+          <t>PRC-22.043/2017-E</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PRC-22.022/2017-D</t>
+          <t>PRC-22.022/2017-C</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PRC-22.022/2017-E</t>
+          <t>PRC-22.022/2017-D</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-B</t>
+          <t>PRC-22.022/2017-E</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PRC-22.025/2017-D</t>
+          <t>PRC-22.025/2017-C</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PRC-22.025/2017-E</t>
+          <t>PRC-22.025/2017-D</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PRC-22.026/2017-B</t>
+          <t>PRC-22.025/2017-E</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PRC-22.040/2017-D</t>
+          <t>PRC-22.040/2017-C</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PRC-22.040/2017-E</t>
+          <t>PRC-22.040/2017-D</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PRC-22.041/2017-B</t>
+          <t>PRC-22.040/2017-E</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PRC-22.028/2017-D</t>
+          <t>PRC-22.028/2017-C</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PRC-22.028/2017-E</t>
+          <t>PRC-22.028/2017-D</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PRC-22.029/2017-B</t>
+          <t>PRC-22.028/2017-E</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PRC-22.027/2017-C</t>
+          <t>PRC-22.027/2017-B</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PRC-22.027/2017-D</t>
+          <t>PRC-22.027/2017-C</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PRC-22.027/2017-E</t>
+          <t>PRC-22.027/2017-D</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PRC-22.028/2017-C</t>
+          <t>PRC-22.027/2017-E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PRC-22.019/2017-D</t>
+          <t>PRC-22.019/2017-C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PRC-22.019/2017-E</t>
+          <t>PRC-22.019/2017-D</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PRC-22.020/2017-C</t>
+          <t>PRC-22.019/2017-E</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PRC-22.018/2017-D</t>
+          <t>PRC-22.018/2017-C</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PRC-22.018/2017-E</t>
+          <t>PRC-22.018/2017-D</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PRC-22.019/2017-C</t>
+          <t>PRC-22.018/2017-E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-D</t>
+          <t>PRC-22.039/2017-C</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-E</t>
+          <t>PRC-22.039/2017-D</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PRC-22.034/2017-D</t>
+          <t>PRC-22.034/2017-C</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PRC-22.034/2017-E</t>
+          <t>PRC-22.034/2017-D</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PRC-22.035/2017-B</t>
+          <t>PRC-22.034/2017-E</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PRC-22.037/2017-C</t>
+          <t>PRC-22.037/2017-B</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PRC-22.037/2017-D</t>
+          <t>PRC-22.037/2017-C</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PRC-22.037/2017-E</t>
+          <t>PRC-22.037/2017-D</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PRC-22.038/2012</t>
+          <t>PRC-22.037/2017-E</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PRC-22.041/2017-C</t>
+          <t>PRC-22.041/2017-B</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PRC-22.041/2017-D</t>
+          <t>PRC-22.041/2017-C</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PRC-22.041/2017-E</t>
+          <t>PRC-22.041/2017-D</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PRC-22.042/2017-B</t>
+          <t>PRC-22.041/2017-E</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PRC-22.038/2017-C</t>
+          <t>PRC-22.038/2017-B</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PRC-22.038/2017-D</t>
+          <t>PRC-22.038/2017-C</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PRC-22.038/2017-E</t>
+          <t>PRC-22.038/2017-D</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-B</t>
+          <t>PRC-22.038/2017-E</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-C</t>
+          <t>PRC-22.032/2017-B</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-D</t>
+          <t>PRC-22.032/2017-C</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-E</t>
+          <t>PRC-22.032/2017-D</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PRC-22.033/2017-C</t>
+          <t>PRC-22.032/2017-E</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PRC-22.031/2017-D</t>
+          <t>PRC-22.031/2017-C</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PRC-22.031/2017-E</t>
+          <t>PRC-22.031/2017-D</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-B</t>
+          <t>PRC-22.031/2017-E</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-C</t>
+          <t>PRC-22.039/2017-B</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PRC-22.040/2017-C</t>
+          <t>PRC-22.039/2017-E</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PRC-22.033/2017-D</t>
+          <t>PRC-22.033/2017-C</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PRC-22.033/2017-E</t>
+          <t>PRC-22.033/2017-D</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PRC-22.034/2017-C</t>
+          <t>PRC-22.033/2017-E</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PRC-22.042/2017-C</t>
+          <t>PRC-22.042/2017-B</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PRC-22.042/2017-D</t>
+          <t>PRC-22.042/2017-C</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PRC-22.042/2017-E</t>
+          <t>PRC-22.042/2017-D</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PRC-22.043/2017-B</t>
+          <t>PRC-22.042/2017-E</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>PRC-22.017/2017-D</t>
+          <t>PRC-22.017/2017-C</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PRC-22.017/2017-E</t>
+          <t>PRC-22.017/2017-D</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PRC-22.017/2018-B</t>
+          <t>PRC-22.017/2017-E</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PRC-22.030/2017-C</t>
+          <t>PRC-22.030/2017-B</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PRC-22.030/2017-D</t>
+          <t>PRC-22.030/2017-C</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PRC-22.030/2017-E</t>
+          <t>PRC-22.030/2017-D</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PRC-22.031/2017-C</t>
+          <t>PRC-22.030/2017-E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-ANO 4</t>
+          <t>PRC-29.008/2017-A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-B</t>
+          <t>PRC-29.008/2017-ANO 4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-D</t>
+          <t>PRC-29.008/2017-B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>PRC-29.008/2017-D</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PRC-29.010/2010-D</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-ANO 4</t>
+          <t>PRC-29.008/2017-A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-B</t>
+          <t>PRC-29.008/2017-ANO 4</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-D</t>
+          <t>PRC-29.008/2017-B</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>PRC-29.008/2017-D</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PRC-29.010/2010-D</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PRC-22.013/2014</t>
+          <t>PRC-22.011/2018</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PRC-24.010/2013</t>
+          <t>PRC-24.005/2018</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>PRC-24.010/2013</t>
+          <t>PRC-24.005/2018</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DC-002/2023</t>
+          <t>DC-002/2022</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PRC-29.007/2017-B</t>
+          <t>PRC-24.017/2018</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PRC-24.017/2018</t>
+          <t>PRC-24.014/2018</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PRC-24.017/2018</t>
+          <t>PRC-24.014/2018</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-C</t>
+          <t>PRC-22.013/2018-B</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-D</t>
+          <t>PRC-22.013/2018-C</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-E</t>
+          <t>PRC-22.013/2018-D</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PRC-22.015/2017-C</t>
+          <t>PRC-22.013/2018-E</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PRC-22.024/2018-B</t>
+          <t>PRC-22.024/2018-A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PRC-22.024/2018-C</t>
+          <t>PRC-22.024/2018-B</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PRC-22.024/2018-D</t>
+          <t>PRC-22.024/2018-C</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>PRC-22.024/2018-E</t>
+          <t>PRC-22.024/2018-D</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PRC-22.025/2017-C</t>
+          <t>PRC-22.024/2018-E</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PRC-22.017/2018-C</t>
+          <t>PRC-22.017/2018-B</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>PRC-22.017/2018-D</t>
+          <t>PRC-22.017/2018-C</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PRC-22.017/2018-E</t>
+          <t>PRC-22.017/2018-D</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PRC-22.018/2011-C</t>
+          <t>PRC-22.017/2018-E</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-C</t>
+          <t>PRC-22.023/2018-B</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-D</t>
+          <t>PRC-22.023/2018-C</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-E</t>
+          <t>PRC-22.023/2018-D</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PRC-22.024/2013</t>
+          <t>PRC-22.023/2018-E</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PRC-22.016/2018-C</t>
+          <t>PRC-22.016/2018-B</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PRC-22.016/2018-D</t>
+          <t>PRC-22.016/2018-C</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>PRC-22.016/2018-E</t>
+          <t>PRC-22.016/2018-D</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PRC-22.017/2017-C</t>
+          <t>PRC-22.016/2018-E</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PRC-22.004/2018-C</t>
+          <t>PRC-22.004/2018-B</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PRC-22.004/2018-D</t>
+          <t>PRC-22.004/2018-C</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PRC-22.004/2018-E</t>
+          <t>PRC-22.004/2018-D</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PRC-22.011/2018</t>
+          <t>PRC-22.004/2018-E</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PRC-22.004/2017</t>
+          <t>PRC-22.003/2019</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 5</t>
+          <t>PRC-24.001/2019-ANO 4</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 6</t>
+          <t>PRC-24.001/2019-ANO 5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PRC-24.004/2019</t>
+          <t>PRC-24.001/2019-ANO 6</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 5</t>
+          <t>PRC-24.001/2019-ANO 4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 6</t>
+          <t>PRC-24.001/2019-ANO 5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PRC-24.004/2019</t>
+          <t>PRC-24.001/2019-ANO 6</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 5</t>
+          <t>PRC-24.001/2019-ANO 4</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 6</t>
+          <t>PRC-24.001/2019-ANO 5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PRC-24.004/2019</t>
+          <t>PRC-24.001/2019-ANO 6</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 5</t>
+          <t>PRC-24.001/2019-ANO 4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PRC-24.001/2019-ANO 6</t>
+          <t>PRC-24.001/2019-ANO 5</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PRC-24.004/2019</t>
+          <t>PRC-24.001/2019-ANO 6</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PRC-24.005/2018</t>
+          <t>PRC-24.004/2019</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PRC-24.005/2018</t>
+          <t>PRC-24.004/2019</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PRC-24.005/2018</t>
+          <t>PRC-24.004/2019</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DM-22.005/2020</t>
+          <t>DM-22.005/2019</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-B</t>
+          <t>DM-22.010/2019-A</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-C</t>
+          <t>DM-22.010/2019-B</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-D</t>
+          <t>DM-22.010/2019-C</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-E</t>
+          <t>DM-22.010/2019-D</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DM-22.010/2020-B</t>
+          <t>DM-22.010/2019-E</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DM-22.006/2019-B</t>
+          <t>DM-22.006/2019-A</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DM-22.006/2019-C</t>
+          <t>DM-22.006/2019-B</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DM-22.006/2019-D</t>
+          <t>DM-22.006/2019-C</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DM-22.006/2020</t>
+          <t>DM-22.006/2019-D</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DC-22.016/2020</t>
+          <t>DC-22.015/2020</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DC-22.015/2020</t>
+          <t>DC-22.013/2020</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DM - 024/2021</t>
+          <t>DI-22.001/2020</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DC-22.019/2020</t>
+          <t>DC-22.018/2020</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DC-22.020/2020</t>
+          <t>DC-22.019/2020</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DC-9439838/2024</t>
+          <t>DC-22.024/2020</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DC-22.018/2020</t>
+          <t>DC-22.017/2020</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DPEI - 028/2023</t>
+          <t>DP-24.007/2020</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DPEI - 028/2023</t>
+          <t>DP-24.007/2020</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DM-22.010/2020-C</t>
+          <t>DM-22.010/2020-B</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DM-22.011/2020</t>
+          <t>DM-22.010/2020-C</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DM-22.010/2020-C</t>
+          <t>DM-22.010/2020-B</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DM-22.011/2020</t>
+          <t>DM-22.010/2020-C</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DM-22.010/2020-C</t>
+          <t>DM-22.010/2020-B</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DM-22.011/2020</t>
+          <t>DM-22.010/2020-C</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DM-22.008/2020-A</t>
+          <t>DM-22.008/2020</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DM-22.008/2020-B</t>
+          <t>DM-22.008/2020-A</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DM-22.008/2020-C</t>
+          <t>DM-22.008/2020-B</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>DM-22.008/2020-D</t>
+          <t>DM-22.008/2020-C</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DM-22.009/2020</t>
+          <t>DM-22.008/2020-D</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DM-22.007/2020-A</t>
+          <t>DM-22.007/2020</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DM-22.007/2020-B</t>
+          <t>DM-22.007/2020-A</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DM-22.007/2020-C</t>
+          <t>DM-22.007/2020-B</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DM-22.007/2020-D</t>
+          <t>DM-22.007/2020-C</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DM-22.008/2020</t>
+          <t>DM-22.007/2020-D</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DM-22.005/2020-A</t>
+          <t>DM-22.005/2020</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DM-22.005/2020-B</t>
+          <t>DM-22.005/2020-A</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DM-22.005/2020-C</t>
+          <t>DM-22.005/2020-B</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>DM-22.005/2020-D</t>
+          <t>DM-22.005/2020-C</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DM-22.006/2019-A</t>
+          <t>DM-22.005/2020-D</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DM-22.004/2020-A</t>
+          <t>DM-22.004/2020</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DM-22.004/2020-B</t>
+          <t>DM-22.004/2020-A</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DM-22.004/2020-C</t>
+          <t>DM-22.004/2020-B</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DM-22.004/2020-D</t>
+          <t>DM-22.004/2020-C</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DM-22.005/2019</t>
+          <t>DM-22.004/2020-D</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DM-22.011/2020-A</t>
+          <t>DM-22.011/2020</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DM-22.011/2020-B</t>
+          <t>DM-22.011/2020-A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DM-22.011/2020-C</t>
+          <t>DM-22.011/2020-B</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DM-22.011/2020-D</t>
+          <t>DM-22.011/2020-C</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DM-22.012/2020</t>
+          <t>DM-22.011/2020-D</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-A</t>
+          <t>DM-22.009/2020</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-B</t>
+          <t>DM-22.009/2020-A</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-C</t>
+          <t>DM-22.009/2020-B</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-D</t>
+          <t>DM-22.009/2020-C</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-A</t>
+          <t>DM-22.009/2020-D</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-A</t>
+          <t>DM-22.012/2020</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-B</t>
+          <t>DM-22.012/2020-A</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-C</t>
+          <t>DM-22.012/2020-B</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-D</t>
+          <t>DM-22.012/2020-C</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DM-22.014/2020</t>
+          <t>DM-22.012/2020-D</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DM-22.003/2020-A</t>
+          <t>DM-22.003/2020</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DM-22.003/2020-B</t>
+          <t>DM-22.003/2020-A</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DM-22.003/2020-C</t>
+          <t>DM-22.003/2020-B</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>DM-22.003/2020-D</t>
+          <t>DM-22.003/2020-C</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>DM-22.004/2020</t>
+          <t>DM-22.003/2020-D</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>DM-22.006/2020-A</t>
+          <t>DM-22.006/2020</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>DM-22.007/2020</t>
+          <t>DM-22.006/2020-A</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DC-018/2022</t>
+          <t>DC-018/2021</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DC-020/2022</t>
+          <t>DC-020/2021</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DG/AMA-009436677/2024</t>
+          <t>DF-012/2021-A</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>DC-006/2022</t>
+          <t>DC-006/2021</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DC-007/2023</t>
+          <t>DC-007/2021</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DC-011/2022</t>
+          <t>DC-011/2021</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>DC-002/2022</t>
+          <t>DC-002/2021</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DC-009/2022</t>
+          <t>DC-009/2021</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DC-016/2022</t>
+          <t>DC-016/2021</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DC-013/2022</t>
+          <t>DC-013/2021</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>DC-012/2022</t>
+          <t>DC-012/2021</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>DC-017/2022</t>
+          <t>DC-017/2021</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>DC-015/2022</t>
+          <t>DC-015/2021</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DC-014/2022</t>
+          <t>DC-014/2021</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>DC-019/2023</t>
+          <t>DC-019/2021</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DP-003/2022</t>
+          <t>DP-003/2021</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DP-002/2022</t>
+          <t>DP-002/2021</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DM-006/2022</t>
+          <t>DM-006/2021</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DM-001/2021</t>
+          <t>DM 014/2021</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DM-011/2022</t>
+          <t>DM-011/2021</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DM-007/2022</t>
+          <t>DM-007/2021</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DM-012/2023</t>
+          <t>DM-012/2021</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DM-004/2022</t>
+          <t>DM-004/2021</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>DM-030/2022</t>
+          <t>DM-030/2021</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DM-029/2022</t>
+          <t>DM-029/2021</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DM-027/2022</t>
+          <t>DM-027/2021</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DM-005/2022</t>
+          <t>DM-005/2021</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DM-028/2022</t>
+          <t>DM-028/2021</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DM-013/2022</t>
+          <t>DM-013/2021</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DM-009/2022</t>
+          <t>DM-009/2021</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DM-017/2022</t>
+          <t>DM-017/2021</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DM-010/2022</t>
+          <t>DM-010/2021</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DM-002/2022</t>
+          <t>DM-002/2021</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DM-003/2022</t>
+          <t>DM-003/2021</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DM-018/2022</t>
+          <t>DM-018/2021</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DM-025/2022</t>
+          <t>DM-025/2021</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DM-023/2022</t>
+          <t>DM-023/2021</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DM-031/2022</t>
+          <t>DM-031/2021</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DM 014/2021</t>
+          <t>DM - 024/2021</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DM-033/2022</t>
+          <t>DM-033/2021</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DM-034/2022</t>
+          <t>DM-034/2021</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>DM-036/2022</t>
+          <t>DM-036/2021</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DM-008/2022</t>
+          <t>DM-008/2021</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DM-035/2022</t>
+          <t>DM-035/2021</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DO-001/2021- B</t>
+          <t>DO-001/2021</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DO-001/2021- B</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DOV-001/2021-A</t>
+          <t>DOV-001/2021</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DOV-001/2021-B</t>
+          <t>DOV-001/2021-A</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DOV-001/2022</t>
+          <t>DOV-001/2021-B</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>DOV-002/2021-A</t>
+          <t>DOV-002/2021</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DOV-002/2021-B</t>
+          <t>DOV-002/2021-A</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DOV-003/2021-A</t>
+          <t>DOV-003/2021</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DOV-003/2021-B</t>
+          <t>DOV-003/2021-A</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DOV-003/2022</t>
+          <t>DOV-003/2021-B</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DOV-004/2021-A</t>
+          <t>DOV-004/2021</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DOV-004/2021-B</t>
+          <t>DOV-004/2021-A</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>DOV-004/2022</t>
+          <t>DOV-004/2021-B</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>DC-004/2024</t>
+          <t>DC-004/2022</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DC-011/2024</t>
+          <t>DC-011/2022</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DC-012/2023</t>
+          <t>DC-012/2022</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>DC-010/2023</t>
+          <t>DC-010/2022</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DC-009/2023</t>
+          <t>DC-009/2022</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DC-015/2023</t>
+          <t>DC-015/2022</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DC-015/2021</t>
+          <t>DC-014/2022</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>DC-013/2023</t>
+          <t>DC-013/2022</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DC-017/2023</t>
+          <t>DC-017/2022</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DC-016/2023</t>
+          <t>DC-016/2022</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>DC-020/2023</t>
+          <t>DC-020/2022</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>DC-018/2023</t>
+          <t>DC-018/2022</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DC-026/2022</t>
+          <t>DC-025/2022</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DC-027/2022</t>
+          <t>DC-026/2022</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DC-024/2022</t>
+          <t>DC-023/2022</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DC-022/2022</t>
+          <t>DC-021/2022</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>DC-003/2023</t>
+          <t>DC-003/2022</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>DC-001/2023</t>
+          <t>DC-001/2022</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>DC-005/2023</t>
+          <t>DC-005/2022</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>DC-022/2022</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DC-025/2022</t>
+          <t>DC-024/2022</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DC-006/2023</t>
+          <t>DC-006/2022</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>DC-008/2023</t>
+          <t>DC-008/2022</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>DP-004/2023</t>
+          <t>DP-004/2022</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DP-005/2023</t>
+          <t>DP-004/2023</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DP-005/2023</t>
+          <t>DP-004/2023</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>DM-005/2023</t>
+          <t>DM-005/2022</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DM-006/2023</t>
+          <t>DM-006/2022</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>DM-013/2023</t>
+          <t>DM-013/2022</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>DM-010/2023</t>
+          <t>DM-010/2022</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>DM-007/2023</t>
+          <t>DM-007/2022</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DM-028/2023</t>
+          <t>DM-028/2022</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>DM-032/2023</t>
+          <t>DM-032/2022</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>DM-020/2023</t>
+          <t>DM-020/2022</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>DM-029/2023</t>
+          <t>DM-029/2022</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -19072,7 +19072,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>DM-022/2023</t>
+          <t>DM-022/2022</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DM-031/2023</t>
+          <t>DM-031/2022</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DM-034/2021</t>
+          <t>DM-033/2022</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DM-037/2022</t>
+          <t>DM-036/2022</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>DM-030/2023</t>
+          <t>DM-030/2022</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>DM-035/2021</t>
+          <t>DM-034/2022</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>DM-023/2023</t>
+          <t>DM-023/2022</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>DM-025/2021</t>
+          <t>DM-024/2022</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>DM-016/2023</t>
+          <t>DM-016/2022</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>DM-038/2022</t>
+          <t>DM-037/2022</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>DM-014/2023</t>
+          <t>DM-014/2022</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>DM-040/2022</t>
+          <t>DM-039/2022</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>DM-015/2023</t>
+          <t>DM-015/2022</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>DM-039/2022</t>
+          <t>DM-038/2022</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>DM-018/2023</t>
+          <t>DM-018/2022</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>DM-017/2023</t>
+          <t>DM-017/2022</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>DM-036/2021</t>
+          <t>DM-035/2022</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>DM-041/2022</t>
+          <t>DM-040/2022</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>DM-025/2023</t>
+          <t>DM-025/2022</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>DM-026/2023</t>
+          <t>DM-026/2022</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>DM-021/2023</t>
+          <t>DM-021/2022</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>DM-019/2023</t>
+          <t>DM-019/2022</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>DM-004/2023</t>
+          <t>DM-004/2022</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>DM-003/2023</t>
+          <t>DM-003/2022</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>DM-002/2023</t>
+          <t>DM-002/2022</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>DM-011/2023</t>
+          <t>DM-011/2022</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>DM-009/2022-A</t>
+          <t>DM-009/2022</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>DM-009/2022-B</t>
+          <t>DM-009/2022-A</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>DM-009/2023</t>
+          <t>DM-009/2022-B</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DOV-001/2022</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>DOV-002/2021</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DOV-001/2022</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>DOV-002/2021</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>DOV-002/2022-A</t>
+          <t>DOV-002/2022</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>DOV-002/2022-B</t>
+          <t>DOV-002/2022-A</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>DOV-003/2021</t>
+          <t>DOV-002/2022-B</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -21252,7 +21252,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>DOV-002/2022-A</t>
+          <t>DOV-002/2022</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>DOV-002/2022-B</t>
+          <t>DOV-002/2022-A</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>DOV-003/2021</t>
+          <t>DOV-002/2022-B</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>DOV-003/2022-A</t>
+          <t>DOV-003/2022</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>DOV-003/2022-B</t>
+          <t>DOV-003/2022-A</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>DOV-004/2021</t>
+          <t>DOV-003/2022-B</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>DOV-003/2022-A</t>
+          <t>DOV-003/2022</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>DOV-003/2022-B</t>
+          <t>DOV-003/2022-A</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>DOV-004/2021</t>
+          <t>DOV-003/2022-B</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>DOV-004/2022-A</t>
+          <t>DOV-004/2022</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>DOV-004/2022-B</t>
+          <t>DOV-004/2022-A</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>DOV-005/2022</t>
+          <t>DOV-004/2022-B</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>DOV-004/2022-A</t>
+          <t>DOV-004/2022</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>DOV-004/2022-B</t>
+          <t>DOV-004/2022-A</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>DOV-005/2022</t>
+          <t>DOV-004/2022-B</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>DOV-005/2022-A</t>
+          <t>DOV-005/2022</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>DOV-005/2022-B</t>
+          <t>DOV-005/2022-A</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>DP-001/2022</t>
+          <t>DOV-005/2022-B</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>DOV-005/2022-A</t>
+          <t>DOV-005/2022</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>DOV-005/2022-B</t>
+          <t>DOV-005/2022-A</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>DP-001/2022</t>
+          <t>DOV-005/2022-B</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>DC-017/2021</t>
+          <t>DC-016/2023</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>DC-019/2021</t>
+          <t>DC-018/2023</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>DC-019/2021</t>
+          <t>DC-018/2023</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>DC-006/2024</t>
+          <t>DC-006/2023</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>DC-007/2024</t>
+          <t>DC-007/2023</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>DC-010/2024</t>
+          <t>DC-010/2023</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>DC-014/2021</t>
+          <t>DC-013/2023</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>DC-016/2021</t>
+          <t>DC-015/2023</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>DC-018/2021</t>
+          <t>DC-017/2023</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>DC-021/2021</t>
+          <t>DC-020/2023</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-009/2023</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>DC-020/2021</t>
+          <t>DC-019/2023</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DC-003/2023</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>DC-001/2024</t>
+          <t>DC-001/2023</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>DC-028/2022</t>
+          <t>DC-027/2022</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DC-002/2023</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>DC-008/2024</t>
+          <t>DC-008/2023</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>DC-22.013/2020</t>
+          <t>DC-028/2022</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>DC-005/2024</t>
+          <t>DC-005/2023</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>DP-006/2023</t>
+          <t>DP-005/2023</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>DP-006/2023</t>
+          <t>DP-005/2023</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>DP-008/2023</t>
+          <t>DP-007/2023</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>DP-009/2023</t>
+          <t>DP-008/2023</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>DP-010/2023</t>
+          <t>DP-009/2023</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>DP-011/2023</t>
+          <t>DP-010/2023</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>DP-012/2023</t>
+          <t>DP-011/2023</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>DP-013/2023</t>
+          <t>DP-012/2023</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>DP-014/2023</t>
+          <t>DP-013/2023</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>DP-015/2023</t>
+          <t>DP-014/2023</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>DP-016/2023</t>
+          <t>DP-015/2023</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>DP-017/2023</t>
+          <t>DP-016/2023</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>DP-018/2023</t>
+          <t>DP-017/2023</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>DP-020/2023</t>
+          <t>DP-018/2023</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24380,7 +24380,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>DP-004/2022</t>
+          <t>DP-003/2023</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -24436,7 +24436,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>DPEI-001/2024</t>
+          <t>DPEI - 028/2023</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>DP-021/2023</t>
+          <t>DP-020/2023</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>DP-021/2023</t>
+          <t>DP-020/2023</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>DP-002/2021</t>
+          <t>DP-001/2023</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>DP-022/2023</t>
+          <t>DP-021/2023</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>DP-002/2021</t>
+          <t>DP-001/2023</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>DP-022/2023</t>
+          <t>DP-021/2023</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>DP-023/2023</t>
+          <t>DP-022/2023</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>DP-024/2023</t>
+          <t>DP-023/2023</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>DP-024/2023</t>
+          <t>DP-023/2023</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>DP-025/2023</t>
+          <t>DP-024/2023</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25052,7 +25052,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>DP-025/2023</t>
+          <t>DP-024/2023</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>DP-026/2023</t>
+          <t>DP-025/2023</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>DP-026/2023</t>
+          <t>DP-025/2023</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>DP-027/2023</t>
+          <t>DP-026/2023</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>DP-027/2023</t>
+          <t>DP-026/2023</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DP-027/2023</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>DP-24.007/2020</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>DP-24.007/2020</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25500,7 +25500,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>DP-007/2023</t>
+          <t>DP-006/2023</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>DM-003/2024</t>
+          <t>DM-003/2023</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -25612,7 +25612,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>DM-004/2024</t>
+          <t>DM-004/2023</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>DM-005/2024</t>
+          <t>DM-005/2023</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -25724,7 +25724,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>DM-024/2022</t>
+          <t>DM-023/2023</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>DM-006/2024</t>
+          <t>DM-006/2023</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>DM-010/2024</t>
+          <t>DM-010/2023</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>DM-007/2024</t>
+          <t>DM-007/2023</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>DM-013/2024</t>
+          <t>DM-013/2023</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DM-008/2023</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -26060,7 +26060,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>DM-011/2024</t>
+          <t>DM-011/2023</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>DM-009/2024</t>
+          <t>DM-009/2023</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -26172,7 +26172,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>DM-017/2024</t>
+          <t>DM-017/2023</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-020/2023</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>DM-015/2024</t>
+          <t>DM-015/2023</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DM-014/2023</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-016/2023</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DM-018/2023</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>DM-026/2023-A</t>
+          <t>DM-026/2023</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>DM-026/2023-B</t>
+          <t>DM-026/2023-A</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -26620,7 +26620,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>DM-027/2021</t>
+          <t>DM-026/2023-B</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>DM-028/2021</t>
+          <t>DM-027/2023</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -26732,7 +26732,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DM-025/2023</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>DM-026/2022</t>
+          <t>DM-025/2023-B</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>DM-029/2023-A</t>
+          <t>DM-029/2023</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>DM-029/2023-B</t>
+          <t>DM-029/2023-A</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>DM-030/2021</t>
+          <t>DM-029/2023-B</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>DM-030/2023-A</t>
+          <t>DM-030/2023</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -27068,7 +27068,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>DM-030/2023-B</t>
+          <t>DM-030/2023-A</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>DM-031/2021</t>
+          <t>DM-030/2023-B</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DM-019/2023</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>DM-022/2022</t>
+          <t>DM-021/2023</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -27292,7 +27292,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-022/2023</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>DM-001/2024</t>
+          <t>DM-001/2023</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>DM-22.003/2020</t>
+          <t>DM-041/2022</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>DM-002/2024</t>
+          <t>DM-002/2023</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>DPEI-9446143</t>
+          <t>DPEI-031/2023</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>DPEI-9446143</t>
+          <t>DPEI-031/2023</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>DPEI-9446143</t>
+          <t>DPEI-031/2023</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -28020,7 +28020,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>DC-9441306/2024</t>
+          <t>DC-9439921/2024</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -28076,7 +28076,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>DC-023/2022</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29084,7 +29084,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -29140,7 +29140,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -29252,7 +29252,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -29308,7 +29308,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -29364,7 +29364,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -29420,7 +29420,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>DF-012/2021-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>DC-003/2021</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>DC-004/2022</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-011/2024</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>DC-9445950/2024</t>
+          <t>DC-9445668/2024</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -29840,7 +29840,7 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L526" t="n">
         <v>2782111.36</v>
@@ -29868,7 +29868,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>DC-002/2021</t>
+          <t>DC-001/2024</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29924,7 +29924,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>DC-9439921/2024</t>
+          <t>DC-9439838/2024</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -29980,7 +29980,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>DC-009/2021</t>
+          <t>DC-008/2024</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -30036,7 +30036,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-9441355/2024 </t>
+          <t>DC-9441306/2024</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>DC-9444080/2024</t>
+          <t xml:space="preserve">DC-9441355/2024 </t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>DC-007/2021</t>
+          <t>DC-006/2024</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -30204,7 +30204,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>DC-9445587/2024</t>
+          <t>DC-9444080/2024</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>DC-005/2022</t>
+          <t>DC-004/2024</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9447109/2024</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -30372,7 +30372,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>DC-008/2021</t>
+          <t>DC-007/2024</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>DC-006/2021</t>
+          <t>DC-005/2024</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -30484,7 +30484,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>DC-011/2021</t>
+          <t>DC-010/2024</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -30540,7 +30540,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>DPEI-006/2024</t>
+          <t>DPEI-005/2024</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>DPEI-002/2024</t>
+          <t>DPEI-001/2024</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -30652,7 +30652,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>DPEI-003/2024</t>
+          <t>DPEI-002/2024</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>DPEI-005/2024</t>
+          <t>DPEI-004/2024</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>DPEI-007/2024</t>
+          <t>DPEI-006/2024</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>DPEI-004/2024</t>
+          <t>DPEI-003/2024</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>DPEI-9447985</t>
+          <t>DPEI-9447050</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>DPEI-9447050</t>
+          <t>DPEI-9446143</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DPEI-007/2024</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>DI-22.001/2020</t>
+          <t>DG/AMA-009436677/2024</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>DM-001/2024-A</t>
+          <t>DM-001/2024</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>DM-001/2024-B</t>
+          <t>DM-001/2024-A</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -31380,7 +31380,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>DM-002/2021</t>
+          <t>DM-001/2024-B</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>DM-9440647/2024</t>
+          <t>DM-9437231</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>DM-9440649/2024</t>
+          <t>DM-9440647/2024</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -31548,7 +31548,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>DM-9440650/2024</t>
+          <t>DM-9440649/2024</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>DM-9440653/2024</t>
+          <t>DM-9440650/2024</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -31660,7 +31660,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>DM-9440654/2024</t>
+          <t>DM-9440653/2024</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>DM-9440655/2024</t>
+          <t>DM-9440654/2024</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -31772,7 +31772,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>DM-9440657/2024</t>
+          <t>DM-9440655/2024</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -31828,7 +31828,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>DM-9440658/2024</t>
+          <t>DM-9440657/2024</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -31884,7 +31884,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>DM-9440661/2024</t>
+          <t>DM-9440658/2024</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>DM-9440662/2024</t>
+          <t>DM-9440661/2024</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>DM-9445781/2024</t>
+          <t>DM-9440662/2024</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>DM-9447057/2024</t>
+          <t>DM-9445821/2024</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -32108,7 +32108,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>DM-9445782/2024</t>
+          <t>DM-9445781/2024</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DM-9447057/2024</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>DM-028/2023-A</t>
+          <t>DM-028/2023</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>DM-028/2023-B</t>
+          <t>DM-028/2023-A</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -32332,7 +32332,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>DM-029/2021</t>
+          <t>DM-028/2023-B</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -32388,7 +32388,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>DM-002/2024-A</t>
+          <t>DM-002/2024</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>DM-002/2024-B</t>
+          <t>DM-002/2024-A</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -32500,7 +32500,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>DM-003/2021</t>
+          <t>DM-002/2024-B</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -32608,7 +32608,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-010/2024</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -32664,7 +32664,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>DM-011/2021</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -32720,7 +32720,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-011/2024</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>DM-012/2021</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>DM-008/2021</t>
+          <t>DM-007/2024</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -32888,7 +32888,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>DM-009/2021</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-009/2024</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>DM-010/2021</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>DM-025/2023-B</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -33168,7 +33168,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>DM-013/2021</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -33280,7 +33280,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>DM-033/2021</t>
+          <t>DM-032/2023</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>DM-032/2022</t>
+          <t>DM-031/2023</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -33392,7 +33392,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>DM-020/2022</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -33448,7 +33448,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>DM-005/2021</t>
+          <t>DM-004/2024</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -33504,7 +33504,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>DM-004/2021</t>
+          <t>DM-003/2024</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>DM-014/2022</t>
+          <t>DM-013/2024</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>DM-007/2021</t>
+          <t>DM-006/2024</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>DM-015/2022</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>DM-019/2022</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -33952,7 +33952,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>DM-017/2021</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>DM-016/2022</t>
+          <t>DM-015/2024</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -34064,7 +34064,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-017/2024</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>DM-018/2021</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>DM-021/2022</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -34288,7 +34288,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -34344,7 +34344,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>DM-023/2021</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>PRC-22.003/2019</t>
+          <t>PO</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -34792,7 +34792,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -34848,7 +34848,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>DC-9459023/2025</t>
+          <t>DC-9459022/2025</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DC-9459023/2025</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -34960,7 +34960,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>DM-001/2023</t>
+          <t>DM-001/2022</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -35072,7 +35072,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>DC-9459022/2025</t>
+          <t>DC-9459021/2025</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -35184,7 +35184,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>DM-001/2022</t>
+          <t>DM-001/2021</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -35296,7 +35296,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -35408,7 +35408,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>DC-010/2021</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>DC-013/2021</t>
+          <t>DC-012/2023</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -35520,7 +35520,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -35576,7 +35576,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -35688,7 +35688,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -35744,7 +35744,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>DC-9458861/2025</t>
+          <t>DC-9458476/2025</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -35912,7 +35912,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -35968,7 +35968,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>DC-9458476/2025</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -36080,7 +36080,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>DC-9459021/2025</t>
+          <t>DC-9458861/2025</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -36136,7 +36136,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -36192,7 +36192,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -36304,7 +36304,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>DC-9481581/2025</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>DPEI-9478941/2025</t>
+          <t>DPEI-9470883</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>DPEI-9470883</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -36584,7 +36584,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DPEI-9447985</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -36692,7 +36692,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>DPEI-9480550/2025</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -36972,7 +36972,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -37028,7 +37028,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -37084,7 +37084,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -37196,7 +37196,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -37252,7 +37252,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -37364,7 +37364,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -37420,7 +37420,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -37476,7 +37476,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>DM-9485591/2025</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -37532,7 +37532,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DM-9485592/2025</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -37644,7 +37644,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>DM-9485592/2025</t>
+          <t>DM-9485591/2025</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -37700,7 +37700,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9454417/2025</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -37756,7 +37756,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -37812,7 +37812,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -37868,7 +37868,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>DM-9454417/2025</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -37980,7 +37980,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -38036,7 +38036,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO009482014/2025</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -38092,7 +38092,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -38255,17 +38255,17 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>DC-001/2022</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -38291,13 +38291,13 @@
         <v>1</v>
       </c>
       <c r="L677" t="n">
-        <v>73884529.66</v>
+        <v>75334510.38</v>
       </c>
       <c r="M677" t="n">
-        <v>73884529.66</v>
+        <v>75334510.38</v>
       </c>
       <c r="N677" t="n">
-        <v>35989998.13</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="678">
@@ -38311,17 +38311,17 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -38347,13 +38347,13 @@
         <v>1</v>
       </c>
       <c r="L678" t="n">
-        <v>73884529.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="M678" t="n">
-        <v>73884529.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="N678" t="n">
-        <v>35989998.13</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="679">
@@ -38362,54 +38362,54 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9468567</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>AEST-9468567/2025</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F679" t="n">
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>66419</v>
+        <v>26883</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I679" t="n">
-        <v>3971</v>
+        <v>3502</v>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K679" t="n">
         <v>1</v>
       </c>
       <c r="L679" t="n">
-        <v>75334510.38</v>
+        <v>12267717.16</v>
       </c>
       <c r="M679" t="n">
-        <v>75334510.38</v>
+        <v>12267717.16</v>
       </c>
       <c r="N679" t="n">
-        <v>45188997.86</v>
+        <v>9200787.869999999</v>
       </c>
     </row>
     <row r="680">
@@ -38418,54 +38418,54 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F680" t="n">
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>66419</v>
+        <v>26883</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I680" t="n">
-        <v>3971</v>
+        <v>3502</v>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K680" t="n">
         <v>1</v>
       </c>
       <c r="L680" t="n">
-        <v>65055206.84</v>
+        <v>12291296.66</v>
       </c>
       <c r="M680" t="n">
-        <v>65055206.84</v>
+        <v>12291296.66</v>
       </c>
       <c r="N680" t="n">
-        <v>32097999.96</v>
+        <v>9218472.49</v>
       </c>
     </row>
     <row r="681">
@@ -38479,17 +38479,17 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>9468567</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>AEST-9468567/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -38515,13 +38515,13 @@
         <v>1</v>
       </c>
       <c r="L681" t="n">
-        <v>12267717.16</v>
+        <v>12197245.67</v>
       </c>
       <c r="M681" t="n">
-        <v>12267717.16</v>
+        <v>12197245.67</v>
       </c>
       <c r="N681" t="n">
-        <v>9200787.869999999</v>
+        <v>9147934.25</v>
       </c>
     </row>
     <row r="682">
@@ -38535,17 +38535,17 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9469794</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -38571,13 +38571,13 @@
         <v>1</v>
       </c>
       <c r="L682" t="n">
-        <v>12291296.66</v>
+        <v>12379211.81</v>
       </c>
       <c r="M682" t="n">
-        <v>12291296.66</v>
+        <v>12379211.81</v>
       </c>
       <c r="N682" t="n">
-        <v>9218472.49</v>
+        <v>9284408.859999999</v>
       </c>
     </row>
     <row r="683">
@@ -38591,17 +38591,17 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9470136</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>AEST-9470136/2025</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -38627,125 +38627,125 @@
         <v>1</v>
       </c>
       <c r="L683" t="n">
-        <v>12197245.67</v>
+        <v>12547127.86</v>
       </c>
       <c r="M683" t="n">
-        <v>12197245.67</v>
+        <v>12547127.86</v>
       </c>
       <c r="N683" t="n">
-        <v>9147934.25</v>
+        <v>9410345.9</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>9469794</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>PROCEC ENGENHARIA S.A</t>
         </is>
       </c>
       <c r="F684" t="n">
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>26883</v>
+        <v>1740</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I684" t="n">
-        <v>3502</v>
+        <v>5107</v>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K684" t="n">
         <v>1</v>
       </c>
       <c r="L684" t="n">
-        <v>12379211.81</v>
+        <v>5887057.98</v>
       </c>
       <c r="M684" t="n">
-        <v>12379211.81</v>
+        <v>5887057.98</v>
       </c>
       <c r="N684" t="n">
-        <v>9284408.859999999</v>
+        <v>5658828.94</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>9470136</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>AEST-9470136/2025</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>OPACO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F685" t="n">
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>26883</v>
+        <v>1740</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I685" t="n">
-        <v>3502</v>
+        <v>5107</v>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K685" t="n">
         <v>1</v>
       </c>
       <c r="L685" t="n">
-        <v>12547127.86</v>
+        <v>28204745.51</v>
       </c>
       <c r="M685" t="n">
-        <v>12547127.86</v>
+        <v>28204745.51</v>
       </c>
       <c r="N685" t="n">
-        <v>9410345.9</v>
+        <v>28204745.51</v>
       </c>
     </row>
     <row r="686">
@@ -38754,12 +38754,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -38769,7 +38769,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>PROCEC ENGENHARIA S.A</t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -38795,13 +38795,13 @@
         <v>1</v>
       </c>
       <c r="L686" t="n">
-        <v>5887057.98</v>
+        <v>4383662.29</v>
       </c>
       <c r="M686" t="n">
-        <v>5887057.98</v>
+        <v>4383662.29</v>
       </c>
       <c r="N686" t="n">
-        <v>5658828.94</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="687">
@@ -38810,22 +38810,18 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>9507997</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>DC-9507997/2026</t>
-        </is>
-      </c>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr">
         <is>
-          <t>OPACO ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -38848,16 +38844,16 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L687" t="n">
-        <v>28204745.51</v>
+        <v>19733859.27</v>
       </c>
       <c r="M687" t="n">
-        <v>28204745.51</v>
+        <v>19733859.26</v>
       </c>
       <c r="N687" t="n">
-        <v>28204745.51</v>
+        <v>16179998.72</v>
       </c>
     </row>
     <row r="688">
@@ -38866,22 +38862,18 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>9507997</t>
-        </is>
-      </c>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>DER-30.014/2025</t>
-        </is>
-      </c>
+          <t>9515457</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr">
         <is>
-          <t>OPACO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -38904,16 +38896,16 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L688" t="n">
-        <v>28204745.51</v>
+        <v>120767701.47</v>
       </c>
       <c r="M688" t="n">
-        <v>28204745.51</v>
+        <v>120767701.47</v>
       </c>
       <c r="N688" t="n">
-        <v>28204745.51</v>
+        <v>87996201.20999999</v>
       </c>
     </row>
     <row r="689">
@@ -38922,22 +38914,18 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>9497471</t>
-        </is>
-      </c>
-      <c r="D689" t="inlineStr">
-        <is>
-          <t>DC-9498666/2026</t>
-        </is>
-      </c>
+          <t>9518140</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
+          <t>CONSTRUTORA SINARCO LTDA</t>
         </is>
       </c>
       <c r="F689" t="n">
@@ -38963,13 +38951,13 @@
         <v>1</v>
       </c>
       <c r="L689" t="n">
-        <v>4383662.29</v>
+        <v>83862492.89</v>
       </c>
       <c r="M689" t="n">
-        <v>4383662.29</v>
+        <v>83862492.89</v>
       </c>
       <c r="N689" t="n">
-        <v>3700000</v>
+        <v>77916642.14</v>
       </c>
     </row>
     <row r="690">
@@ -38978,22 +38966,22 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -39016,16 +39004,16 @@
         </is>
       </c>
       <c r="K690" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L690" t="n">
-        <v>19733859.27</v>
+        <v>2962697.76</v>
       </c>
       <c r="M690" t="n">
-        <v>19733859.26</v>
+        <v>2962697.76</v>
       </c>
       <c r="N690" t="n">
-        <v>16179998.72</v>
+        <v>2962697.76</v>
       </c>
     </row>
     <row r="691">
@@ -39034,22 +39022,18 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>9515457</t>
-        </is>
-      </c>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA SINARCO LTDA</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -39072,16 +39056,16 @@
         </is>
       </c>
       <c r="K691" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L691" t="n">
-        <v>120767701.47</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="M691" t="n">
-        <v>120767701.47</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="N691" t="n">
-        <v>87996201.20999999</v>
+        <v>61779996.11</v>
       </c>
     </row>
     <row r="692">
@@ -39090,22 +39074,18 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301520 000017/2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>9518140</t>
-        </is>
-      </c>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SINARCO LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -39131,13 +39111,13 @@
         <v>1</v>
       </c>
       <c r="L692" t="n">
-        <v>83862492.89</v>
+        <v>6602550.32</v>
       </c>
       <c r="M692" t="n">
-        <v>83862492.89</v>
+        <v>6602550.32</v>
       </c>
       <c r="N692" t="n">
-        <v>77916642.14</v>
+        <v>5995000</v>
       </c>
     </row>
     <row r="693">
@@ -39146,22 +39126,18 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>9498942</t>
-        </is>
-      </c>
-      <c r="D693" t="inlineStr">
-        <is>
-          <t>DC-012/2021</t>
-        </is>
-      </c>
+          <t>9519295</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -39187,13 +39163,13 @@
         <v>1</v>
       </c>
       <c r="L693" t="n">
-        <v>2962697.76</v>
+        <v>37610115.71</v>
       </c>
       <c r="M693" t="n">
-        <v>2962697.76</v>
+        <v>37610115.71</v>
       </c>
       <c r="N693" t="n">
-        <v>2962697.76</v>
+        <v>34487308.95</v>
       </c>
     </row>
     <row r="694">
@@ -39202,22 +39178,18 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>9518942</t>
-        </is>
-      </c>
-      <c r="D694" t="inlineStr">
-        <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
+          <t>9519020</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SINARCO LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F694" t="n">
@@ -39243,13 +39215,13 @@
         <v>1</v>
       </c>
       <c r="L694" t="n">
-        <v>83450845.04000001</v>
+        <v>8481152.01</v>
       </c>
       <c r="M694" t="n">
-        <v>83450845.04000001</v>
+        <v>8481152.01</v>
       </c>
       <c r="N694" t="n">
-        <v>61779996.11</v>
+        <v>7088404.99</v>
       </c>
     </row>
     <row r="695">
@@ -39258,22 +39230,22 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2301520 000017/2026</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>9519017</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>DC-9519017/2026</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F695" t="n">
@@ -39299,13 +39271,13 @@
         <v>1</v>
       </c>
       <c r="L695" t="n">
-        <v>6602550.32</v>
+        <v>15970367.44</v>
       </c>
       <c r="M695" t="n">
-        <v>6602550.32</v>
+        <v>15970367.44</v>
       </c>
       <c r="N695" t="n">
-        <v>5995000</v>
+        <v>12246077.75</v>
       </c>
     </row>
     <row r="696">
@@ -39314,54 +39286,54 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F696" t="n">
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I696" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K696" t="n">
         <v>1</v>
       </c>
       <c r="L696" t="n">
-        <v>37610115.71</v>
+        <v>7420078.73</v>
       </c>
       <c r="M696" t="n">
-        <v>37610115.71</v>
+        <v>7420078.73</v>
       </c>
       <c r="N696" t="n">
-        <v>34487308.95</v>
+        <v>6677404.33</v>
       </c>
     </row>
     <row r="697">
@@ -39370,54 +39342,54 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>9519020</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F697" t="n">
         <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I697" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K697" t="n">
         <v>1</v>
       </c>
       <c r="L697" t="n">
-        <v>8481152.01</v>
+        <v>3563439</v>
       </c>
       <c r="M697" t="n">
-        <v>8481152.01</v>
+        <v>3563439</v>
       </c>
       <c r="N697" t="n">
-        <v>7088404.99</v>
+        <v>3028048.96</v>
       </c>
     </row>
     <row r="698">
@@ -39426,22 +39398,22 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>CONSTRUTORA CONTORNO LTDA</t>
         </is>
       </c>
       <c r="F698" t="n">
@@ -39467,13 +39439,13 @@
         <v>1</v>
       </c>
       <c r="L698" t="n">
-        <v>15970367.44</v>
+        <v>44004328.59</v>
       </c>
       <c r="M698" t="n">
-        <v>15970367.44</v>
+        <v>44004328.59</v>
       </c>
       <c r="N698" t="n">
-        <v>12246077.75</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="699">
@@ -39482,54 +39454,54 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F699" t="n">
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I699" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K699" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L699" t="n">
-        <v>7420078.73</v>
+        <v>11144418.23</v>
       </c>
       <c r="M699" t="n">
-        <v>7420078.73</v>
+        <v>11144418.22</v>
       </c>
       <c r="N699" t="n">
-        <v>6677404.33</v>
+        <v>9814000</v>
       </c>
     </row>
     <row r="700">
@@ -39538,54 +39510,50 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>9492715</t>
-        </is>
-      </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>DC-9492718/2025</t>
-        </is>
-      </c>
+          <t>9519595</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>L.M. EMPREENDIMENTOS E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F700" t="n">
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I700" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K700" t="n">
         <v>1</v>
       </c>
       <c r="L700" t="n">
-        <v>3563439</v>
+        <v>79427050.02</v>
       </c>
       <c r="M700" t="n">
-        <v>3563439</v>
+        <v>79427050.02</v>
       </c>
       <c r="N700" t="n">
-        <v>3028048.96</v>
+        <v>69497864.40000001</v>
       </c>
     </row>
     <row r="701">
@@ -39594,22 +39562,18 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>9493529</t>
-        </is>
-      </c>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>DC-9495596/2026</t>
-        </is>
-      </c>
+          <t>9519740</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CONTORNO LTDA</t>
+          <t>DIFFERENCIAL ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F701" t="n">
@@ -39635,13 +39599,13 @@
         <v>1</v>
       </c>
       <c r="L701" t="n">
-        <v>44004328.59</v>
+        <v>33864867.02</v>
       </c>
       <c r="M701" t="n">
-        <v>44004328.59</v>
+        <v>33864867.02</v>
       </c>
       <c r="N701" t="n">
-        <v>37600000</v>
+        <v>27896726.26</v>
       </c>
     </row>
     <row r="702">
@@ -39650,54 +39614,50 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="D702" t="inlineStr">
-        <is>
-          <t>DC-9505062/2026</t>
-        </is>
-      </c>
+          <t>9498666</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F702" t="n">
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I702" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K702" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L702" t="n">
-        <v>11144418.23</v>
+        <v>32765091.84</v>
       </c>
       <c r="M702" t="n">
-        <v>11144418.22</v>
+        <v>32765091.84</v>
       </c>
       <c r="N702" t="n">
-        <v>9814000</v>
+        <v>23052682.68</v>
       </c>
     </row>
     <row r="703">
@@ -39706,54 +39666,50 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2301520 000037/2026</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>9519595</t>
-        </is>
-      </c>
-      <c r="D703" t="inlineStr">
-        <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
+          <t>9501894</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
-          <t>L.M. EMPREENDIMENTOS E CONSULTORIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F703" t="n">
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I703" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K703" t="n">
         <v>1</v>
       </c>
       <c r="L703" t="n">
-        <v>79427050.02</v>
+        <v>6323844.01</v>
       </c>
       <c r="M703" t="n">
-        <v>79427050.02</v>
+        <v>6323844.01</v>
       </c>
       <c r="N703" t="n">
-        <v>69497864.40000001</v>
+        <v>4742883</v>
       </c>
     </row>
     <row r="704">
@@ -39762,22 +39718,22 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>DIFFERENCIAL ENGENHARIA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -39803,13 +39759,13 @@
         <v>1</v>
       </c>
       <c r="L704" t="n">
-        <v>33864867.02</v>
+        <v>3965005.14</v>
       </c>
       <c r="M704" t="n">
-        <v>33864867.02</v>
+        <v>3965005.14</v>
       </c>
       <c r="N704" t="n">
-        <v>27896726.26</v>
+        <v>2961858.83</v>
       </c>
     </row>
     <row r="705">
@@ -39818,50 +39774,50 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>9498666</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F705" t="n">
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I705" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K705" t="n">
         <v>1</v>
       </c>
       <c r="L705" t="n">
-        <v>32765091.84</v>
+        <v>151298828.22</v>
       </c>
       <c r="M705" t="n">
-        <v>32765091.84</v>
+        <v>151298828.22</v>
       </c>
       <c r="N705" t="n">
-        <v>23052682.68</v>
+        <v>120800000</v>
       </c>
     </row>
     <row r="706">
@@ -39870,54 +39826,54 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
         </is>
       </c>
       <c r="F706" t="n">
         <v>1</v>
       </c>
       <c r="G706" t="n">
-        <v>10774</v>
+        <v>115827</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
         </is>
       </c>
       <c r="I706" t="n">
-        <v>5106</v>
+        <v>3973</v>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K706" t="n">
         <v>1</v>
       </c>
       <c r="L706" t="n">
-        <v>6323844.01</v>
+        <v>48044257.29</v>
       </c>
       <c r="M706" t="n">
-        <v>6323844.01</v>
+        <v>48044257.29</v>
       </c>
       <c r="N706" t="n">
-        <v>4742883</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="707">
@@ -39926,54 +39882,54 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F707" t="n">
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>1740</v>
+        <v>23167</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I707" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K707" t="n">
         <v>1</v>
       </c>
       <c r="L707" t="n">
-        <v>3965005.14</v>
+        <v>1904028.2</v>
       </c>
       <c r="M707" t="n">
-        <v>3965005.14</v>
+        <v>1904028.2</v>
       </c>
       <c r="N707" t="n">
-        <v>2961858.83</v>
+        <v>1768342.65</v>
       </c>
     </row>
     <row r="708">
@@ -39982,33 +39938,33 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F708" t="n">
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>1740</v>
+        <v>1872</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I708" t="n">
@@ -40023,13 +39979,13 @@
         <v>1</v>
       </c>
       <c r="L708" t="n">
-        <v>151298828.22</v>
+        <v>99982008.22</v>
       </c>
       <c r="M708" t="n">
-        <v>151298828.22</v>
+        <v>99982008.22</v>
       </c>
       <c r="N708" t="n">
-        <v>120800000</v>
+        <v>64984305.34</v>
       </c>
     </row>
     <row r="709">
@@ -40038,54 +39994,50 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
+          <t>9512044</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr">
         <is>
-          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F709" t="n">
         <v>1</v>
       </c>
       <c r="G709" t="n">
-        <v>115827</v>
+        <v>1872</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I709" t="n">
-        <v>3973</v>
+        <v>5107</v>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K709" t="n">
         <v>1</v>
       </c>
       <c r="L709" t="n">
-        <v>48044257.29</v>
+        <v>13602005.38</v>
       </c>
       <c r="M709" t="n">
-        <v>48044257.29</v>
+        <v>13602005.38</v>
       </c>
       <c r="N709" t="n">
-        <v>36033198.22</v>
+        <v>11358610.11</v>
       </c>
     </row>
     <row r="710">
@@ -40094,54 +40046,50 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2301617 000004/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>9502187</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F710" t="n">
         <v>1</v>
       </c>
       <c r="G710" t="n">
-        <v>23167</v>
+        <v>1872</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I710" t="n">
-        <v>3999</v>
+        <v>5107</v>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K710" t="n">
         <v>1</v>
       </c>
       <c r="L710" t="n">
-        <v>1904028.2</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="M710" t="n">
-        <v>1904028.2</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="N710" t="n">
-        <v>1768342.65</v>
+        <v>44002130</v>
       </c>
     </row>
     <row r="711">
@@ -40150,22 +40098,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>CONSTRUTORA ITAMARACA LTDA</t>
         </is>
       </c>
       <c r="F711" t="n">
@@ -40191,13 +40139,13 @@
         <v>1</v>
       </c>
       <c r="L711" t="n">
-        <v>99982008.22</v>
+        <v>11437822.96</v>
       </c>
       <c r="M711" t="n">
-        <v>99982008.22</v>
+        <v>11437822.96</v>
       </c>
       <c r="N711" t="n">
-        <v>64984305.34</v>
+        <v>10619818.83</v>
       </c>
     </row>
     <row r="712">
@@ -40206,22 +40154,22 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>9512044</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F712" t="n">
@@ -40247,13 +40195,13 @@
         <v>1</v>
       </c>
       <c r="L712" t="n">
-        <v>13602005.38</v>
+        <v>19019690.63</v>
       </c>
       <c r="M712" t="n">
-        <v>13602005.38</v>
+        <v>19019690.63</v>
       </c>
       <c r="N712" t="n">
-        <v>11358610.11</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="713">
@@ -40262,22 +40210,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -40303,13 +40251,13 @@
         <v>1</v>
       </c>
       <c r="L713" t="n">
-        <v>73340224.20999999</v>
+        <v>6305546.68</v>
       </c>
       <c r="M713" t="n">
-        <v>73340224.20999999</v>
+        <v>6305546.68</v>
       </c>
       <c r="N713" t="n">
-        <v>44002130</v>
+        <v>4557819.64</v>
       </c>
     </row>
     <row r="714">
@@ -40318,54 +40266,54 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITAMARACA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F714" t="n">
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I714" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K714" t="n">
         <v>1</v>
       </c>
       <c r="L714" t="n">
-        <v>11437822.96</v>
+        <v>8281446.48</v>
       </c>
       <c r="M714" t="n">
-        <v>11437822.96</v>
+        <v>0</v>
       </c>
       <c r="N714" t="n">
-        <v>10619818.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -40374,12 +40322,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -40389,39 +40337,39 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F715" t="n">
         <v>1</v>
       </c>
       <c r="G715" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I715" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K715" t="n">
         <v>1</v>
       </c>
       <c r="L715" t="n">
-        <v>19019690.63</v>
+        <v>8281446.48</v>
       </c>
       <c r="M715" t="n">
-        <v>19019690.63</v>
+        <v>8281446.48</v>
       </c>
       <c r="N715" t="n">
-        <v>14264750.82</v>
+        <v>5342582.88</v>
       </c>
     </row>
     <row r="716">
@@ -40430,22 +40378,18 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>9493202</t>
-        </is>
-      </c>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>DM-9497685/2026</t>
-        </is>
-      </c>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F716" t="n">
@@ -40471,13 +40415,13 @@
         <v>1</v>
       </c>
       <c r="L716" t="n">
-        <v>6305546.68</v>
+        <v>16936267.4</v>
       </c>
       <c r="M716" t="n">
-        <v>6305546.68</v>
+        <v>16936267.4</v>
       </c>
       <c r="N716" t="n">
-        <v>4557819.64</v>
+        <v>14124998.39</v>
       </c>
     </row>
     <row r="717">
@@ -40486,54 +40430,50 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000028/2025</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>9502116</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>DM-9504058/2026</t>
-        </is>
-      </c>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F717" t="n">
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I717" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K717" t="n">
         <v>1</v>
       </c>
       <c r="L717" t="n">
-        <v>8281446.48</v>
+        <v>64979801.54</v>
       </c>
       <c r="M717" t="n">
-        <v>0</v>
+        <v>64979801.54</v>
       </c>
       <c r="N717" t="n">
-        <v>0</v>
+        <v>46640000</v>
       </c>
     </row>
     <row r="718">
@@ -40542,12 +40482,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -40557,39 +40497,39 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="F718" t="n">
         <v>1</v>
       </c>
       <c r="G718" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I718" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K718" t="n">
         <v>1</v>
       </c>
       <c r="L718" t="n">
-        <v>8281446.48</v>
+        <v>28640371.76</v>
       </c>
       <c r="M718" t="n">
-        <v>8281446.48</v>
+        <v>28640371.76</v>
       </c>
       <c r="N718" t="n">
-        <v>5342582.88</v>
+        <v>19798000</v>
       </c>
     </row>
     <row r="719">
@@ -40598,89 +40538,83 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="F719" t="n">
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>1872</v>
+        <v>66419</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I719" t="n">
-        <v>5107</v>
+        <v>3971</v>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K719" t="n">
         <v>1</v>
       </c>
       <c r="L719" t="n">
-        <v>16936267.4</v>
+        <v>64031795.21</v>
       </c>
       <c r="M719" t="n">
-        <v>16936267.4</v>
+        <v>64031795.21</v>
       </c>
       <c r="N719" t="n">
-        <v>14124998.39</v>
+        <v>31699998.96</v>
       </c>
     </row>
     <row r="720">
-      <c r="A720" t="n">
-        <v>2026</v>
-      </c>
+      <c r="A720" t="inlineStr"/>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301520 000001/2020</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>9519034</t>
-        </is>
-      </c>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F720" t="n">
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I720" t="n">
@@ -40695,48 +40629,42 @@
         <v>1</v>
       </c>
       <c r="L720" t="n">
-        <v>64979801.54</v>
+        <v>4668587.23</v>
       </c>
       <c r="M720" t="n">
-        <v>64979801.54</v>
+        <v>0</v>
       </c>
       <c r="N720" t="n">
-        <v>46640000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
-      <c r="A721" t="n">
-        <v>2026</v>
-      </c>
+      <c r="A721" t="inlineStr"/>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301520 000001/2021</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>9504058</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr">
-        <is>
-          <t>DO-001/2021</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F721" t="n">
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I721" t="n">
@@ -40751,76 +40679,70 @@
         <v>1</v>
       </c>
       <c r="L721" t="n">
-        <v>28640371.76</v>
+        <v>16217686.32</v>
       </c>
       <c r="M721" t="n">
-        <v>28640371.76</v>
+        <v>16217686.32</v>
       </c>
       <c r="N721" t="n">
-        <v>19798000</v>
+        <v>12796116.03</v>
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="n">
-        <v>2026</v>
-      </c>
+      <c r="A722" t="inlineStr"/>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>9493205</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>DOV-001/2021</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F722" t="n">
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>66419</v>
+        <v>1740</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I722" t="n">
-        <v>3971</v>
+        <v>5107</v>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K722" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L722" t="n">
-        <v>64031795.21</v>
+        <v>18465630.31</v>
       </c>
       <c r="M722" t="n">
-        <v>64031795.21</v>
+        <v>0</v>
       </c>
       <c r="N722" t="n">
-        <v>31699998.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr"/>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2301520 000001/2020</t>
+          <t>2301520 000006/2020</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -40831,18 +40753,18 @@
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F723" t="n">
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>1740</v>
+        <v>1872</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I723" t="n">
@@ -40857,20 +40779,20 @@
         <v>1</v>
       </c>
       <c r="L723" t="n">
-        <v>4668587.23</v>
+        <v>46371045.53</v>
       </c>
       <c r="M723" t="n">
-        <v>0</v>
+        <v>46371045.53</v>
       </c>
       <c r="N723" t="n">
-        <v>0</v>
+        <v>34303736.06</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr"/>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2301520 000001/2021</t>
+          <t>2301520 000013/2021</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -40881,7 +40803,7 @@
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F724" t="n">
@@ -40907,20 +40829,20 @@
         <v>1</v>
       </c>
       <c r="L724" t="n">
-        <v>16217686.32</v>
+        <v>2022624.54</v>
       </c>
       <c r="M724" t="n">
-        <v>16217686.32</v>
+        <v>2022624.54</v>
       </c>
       <c r="N724" t="n">
-        <v>12796116.03</v>
+        <v>1704806.45</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr"/>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -40931,46 +40853,46 @@
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F725" t="n">
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>1740</v>
+        <v>108600</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I725" t="n">
-        <v>5107</v>
+        <v>3964</v>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K725" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L725" t="n">
-        <v>18465630.31</v>
+        <v>540000</v>
       </c>
       <c r="M725" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="N725" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr"/>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2301520 000006/2020</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -40981,46 +40903,46 @@
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F726" t="n">
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>1872</v>
+        <v>108600</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I726" t="n">
-        <v>5107</v>
+        <v>3964</v>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K726" t="n">
         <v>1</v>
       </c>
       <c r="L726" t="n">
-        <v>46371045.53</v>
+        <v>454999.67</v>
       </c>
       <c r="M726" t="n">
-        <v>46371045.53</v>
+        <v>454999.67</v>
       </c>
       <c r="N726" t="n">
-        <v>34303736.06</v>
+        <v>454999.67</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr"/>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2301520 000013/2021</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -41031,39 +40953,39 @@
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F727" t="n">
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>1740</v>
+        <v>108600</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I727" t="n">
-        <v>5107</v>
+        <v>3964</v>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K727" t="n">
         <v>1</v>
       </c>
       <c r="L727" t="n">
-        <v>2022624.54</v>
+        <v>508997.33</v>
       </c>
       <c r="M727" t="n">
-        <v>2022624.54</v>
+        <v>508997.33</v>
       </c>
       <c r="N727" t="n">
-        <v>1704806.45</v>
+        <v>508997.33</v>
       </c>
     </row>
     <row r="728">
@@ -41081,7 +41003,7 @@
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -41107,13 +41029,13 @@
         <v>1</v>
       </c>
       <c r="L728" t="n">
-        <v>540000</v>
+        <v>386990</v>
       </c>
       <c r="M728" t="n">
-        <v>540000</v>
+        <v>386990</v>
       </c>
       <c r="N728" t="n">
-        <v>540000</v>
+        <v>386990</v>
       </c>
     </row>
     <row r="729">
@@ -41131,7 +41053,7 @@
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F729" t="n">
@@ -41157,13 +41079,13 @@
         <v>1</v>
       </c>
       <c r="L729" t="n">
-        <v>454999.67</v>
+        <v>384900</v>
       </c>
       <c r="M729" t="n">
-        <v>454999.67</v>
+        <v>384900</v>
       </c>
       <c r="N729" t="n">
-        <v>454999.67</v>
+        <v>384900</v>
       </c>
     </row>
     <row r="730">
@@ -41181,7 +41103,7 @@
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F730" t="n">
@@ -41207,20 +41129,20 @@
         <v>1</v>
       </c>
       <c r="L730" t="n">
-        <v>508997.33</v>
+        <v>566000</v>
       </c>
       <c r="M730" t="n">
-        <v>508997.33</v>
+        <v>566000</v>
       </c>
       <c r="N730" t="n">
-        <v>508997.33</v>
+        <v>566000</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr"/>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -41231,46 +41153,46 @@
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F731" t="n">
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>108600</v>
+        <v>23159</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I731" t="n">
-        <v>3964</v>
+        <v>3981</v>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K731" t="n">
         <v>1</v>
       </c>
       <c r="L731" t="n">
-        <v>386990</v>
+        <v>1947867.48</v>
       </c>
       <c r="M731" t="n">
-        <v>386990</v>
+        <v>0</v>
       </c>
       <c r="N731" t="n">
-        <v>386990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr"/>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -41281,46 +41203,46 @@
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F732" t="n">
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>108600</v>
+        <v>23159</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I732" t="n">
-        <v>3964</v>
+        <v>3981</v>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K732" t="n">
         <v>1</v>
       </c>
       <c r="L732" t="n">
-        <v>384900</v>
+        <v>2235628.88</v>
       </c>
       <c r="M732" t="n">
-        <v>384900</v>
+        <v>0</v>
       </c>
       <c r="N732" t="n">
-        <v>384900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr"/>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -41331,46 +41253,46 @@
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F733" t="n">
         <v>1</v>
       </c>
       <c r="G733" t="n">
-        <v>108600</v>
+        <v>23159</v>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I733" t="n">
-        <v>3964</v>
+        <v>3981</v>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K733" t="n">
         <v>1</v>
       </c>
       <c r="L733" t="n">
-        <v>566000</v>
+        <v>2251859.48</v>
       </c>
       <c r="M733" t="n">
-        <v>566000</v>
+        <v>0</v>
       </c>
       <c r="N733" t="n">
-        <v>566000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr"/>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301762 000005/2023</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -41381,46 +41303,46 @@
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="F734" t="n">
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>23159</v>
+        <v>1872</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I734" t="n">
-        <v>3981</v>
+        <v>5107</v>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K734" t="n">
         <v>1</v>
       </c>
       <c r="L734" t="n">
-        <v>1947867.48</v>
+        <v>10768247.16</v>
       </c>
       <c r="M734" t="n">
-        <v>0</v>
+        <v>10768247.16</v>
       </c>
       <c r="N734" t="n">
-        <v>0</v>
+        <v>8795462.050000001</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr"/>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301762 000016/2017</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -41431,46 +41353,46 @@
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F735" t="n">
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>23159</v>
+        <v>1872</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I735" t="n">
-        <v>3981</v>
+        <v>5107</v>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K735" t="n">
         <v>1</v>
       </c>
       <c r="L735" t="n">
-        <v>2235628.88</v>
+        <v>24277046.87</v>
       </c>
       <c r="M735" t="n">
-        <v>0</v>
+        <v>24277046.87</v>
       </c>
       <c r="N735" t="n">
-        <v>0</v>
+        <v>24277046.87</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr"/>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301762 000016/2017</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -41481,188 +41403,38 @@
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F736" t="n">
         <v>1</v>
       </c>
       <c r="G736" t="n">
-        <v>23159</v>
+        <v>1872</v>
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I736" t="n">
-        <v>3981</v>
+        <v>5107</v>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K736" t="n">
         <v>1</v>
       </c>
       <c r="L736" t="n">
-        <v>2251859.48</v>
+        <v>12102613.88</v>
       </c>
       <c r="M736" t="n">
-        <v>0</v>
+        <v>12102613.88</v>
       </c>
       <c r="N736" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr"/>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>2301762 000005/2023</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D737" t="inlineStr"/>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
-        </is>
-      </c>
-      <c r="F737" t="n">
-        <v>1</v>
-      </c>
-      <c r="G737" t="n">
-        <v>1872</v>
-      </c>
-      <c r="H737" t="inlineStr">
-        <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
-        </is>
-      </c>
-      <c r="I737" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J737" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K737" t="n">
-        <v>1</v>
-      </c>
-      <c r="L737" t="n">
-        <v>10768247.16</v>
-      </c>
-      <c r="M737" t="n">
-        <v>10768247.16</v>
-      </c>
-      <c r="N737" t="n">
-        <v>8795462.050000001</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr"/>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>2301762 000016/2017</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D738" t="inlineStr"/>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
-        </is>
-      </c>
-      <c r="F738" t="n">
-        <v>1</v>
-      </c>
-      <c r="G738" t="n">
-        <v>1872</v>
-      </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
-        </is>
-      </c>
-      <c r="I738" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J738" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K738" t="n">
-        <v>1</v>
-      </c>
-      <c r="L738" t="n">
-        <v>24277046.87</v>
-      </c>
-      <c r="M738" t="n">
-        <v>24277046.87</v>
-      </c>
-      <c r="N738" t="n">
-        <v>24277046.87</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr"/>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>2301762 000016/2017</t>
-        </is>
-      </c>
-      <c r="C739" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr">
-        <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
-        </is>
-      </c>
-      <c r="F739" t="n">
-        <v>1</v>
-      </c>
-      <c r="G739" t="n">
-        <v>1872</v>
-      </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
-        </is>
-      </c>
-      <c r="I739" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J739" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K739" t="n">
-        <v>1</v>
-      </c>
-      <c r="L739" t="n">
-        <v>12102613.88</v>
-      </c>
-      <c r="M739" t="n">
-        <v>12102613.88</v>
-      </c>
-      <c r="N739" t="n">
         <v>12102613.88</v>
       </c>
     </row>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N736"/>
+  <dimension ref="A1:N739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32883,17 +32883,17 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -32919,13 +32919,13 @@
         <v>1</v>
       </c>
       <c r="L581" t="n">
-        <v>45388427.46</v>
+        <v>59075097</v>
       </c>
       <c r="M581" t="n">
-        <v>45388427.46</v>
+        <v>59075097</v>
       </c>
       <c r="N581" t="n">
-        <v>31307061.77</v>
+        <v>41801980.63</v>
       </c>
     </row>
     <row r="582">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -32995,17 +32995,17 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>DM-009/2024</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F583" t="n">
@@ -33031,13 +33031,13 @@
         <v>1</v>
       </c>
       <c r="L583" t="n">
-        <v>49516428.28</v>
+        <v>45388427.46</v>
       </c>
       <c r="M583" t="n">
-        <v>49516428.28</v>
+        <v>45388427.46</v>
       </c>
       <c r="N583" t="n">
-        <v>30648355.12</v>
+        <v>31307061.77</v>
       </c>
     </row>
     <row r="584">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-009/2024</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -33163,17 +33163,17 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>DM-012/2024</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ZAG LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F586" t="n">
@@ -33199,13 +33199,13 @@
         <v>1</v>
       </c>
       <c r="L586" t="n">
-        <v>42427903.76</v>
+        <v>49516428.28</v>
       </c>
       <c r="M586" t="n">
-        <v>42427903.76</v>
+        <v>49516428.28</v>
       </c>
       <c r="N586" t="n">
-        <v>29715772.52</v>
+        <v>30648355.12</v>
       </c>
     </row>
     <row r="587">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2301762 000039/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>9410180</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>DM-032/2023</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>CONSTRUTORA ZAG LTDA</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -33311,13 +33311,13 @@
         <v>1</v>
       </c>
       <c r="L588" t="n">
-        <v>51900209.21</v>
+        <v>42427903.76</v>
       </c>
       <c r="M588" t="n">
-        <v>51900209.21</v>
+        <v>42427903.76</v>
       </c>
       <c r="N588" t="n">
-        <v>43983527.2</v>
+        <v>29715772.52</v>
       </c>
     </row>
     <row r="589">
@@ -33326,22 +33326,22 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2301762 000041/2023</t>
+          <t>2301762 000039/2023</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>9410175</t>
+          <t>9410180</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>DM-031/2023</t>
+          <t>DM-032/2023</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -33367,13 +33367,13 @@
         <v>1</v>
       </c>
       <c r="L589" t="n">
-        <v>17443062.11</v>
+        <v>51900209.21</v>
       </c>
       <c r="M589" t="n">
-        <v>17443062.11</v>
+        <v>51900209.21</v>
       </c>
       <c r="N589" t="n">
-        <v>16521453.91</v>
+        <v>43983527.2</v>
       </c>
     </row>
     <row r="590">
@@ -33382,22 +33382,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>2301762 000041/2023</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9410175</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DM-031/2023</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -33420,16 +33420,16 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L590" t="n">
-        <v>11996710.85</v>
+        <v>17443062.11</v>
       </c>
       <c r="M590" t="n">
-        <v>11996710.85</v>
+        <v>17443062.11</v>
       </c>
       <c r="N590" t="n">
-        <v>8049000</v>
+        <v>16521453.91</v>
       </c>
     </row>
     <row r="591">
@@ -33438,22 +33438,22 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2301762 000046/2023</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>9413969</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>DM-004/2024</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -33476,16 +33476,16 @@
         </is>
       </c>
       <c r="K591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L591" t="n">
-        <v>1009319.98</v>
+        <v>11996710.85</v>
       </c>
       <c r="M591" t="n">
-        <v>1009319.98</v>
+        <v>11996710.85</v>
       </c>
       <c r="N591" t="n">
-        <v>948728.78</v>
+        <v>8049000</v>
       </c>
     </row>
     <row r="592">
@@ -33494,22 +33494,22 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2301762 000048/2023</t>
+          <t>2301762 000046/2023</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>9412570</t>
+          <t>9413969</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>DM-003/2024</t>
+          <t>DM-004/2024</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -33535,13 +33535,13 @@
         <v>1</v>
       </c>
       <c r="L592" t="n">
-        <v>50023008.61</v>
+        <v>1009319.98</v>
       </c>
       <c r="M592" t="n">
-        <v>50023008.61</v>
+        <v>1009319.98</v>
       </c>
       <c r="N592" t="n">
-        <v>46770710.65</v>
+        <v>948728.78</v>
       </c>
     </row>
     <row r="593">
@@ -33550,22 +33550,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2301762 000049/2023</t>
+          <t>2301762 000048/2023</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>9423384</t>
+          <t>9412570</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>DM-013/2024</t>
+          <t>DM-003/2024</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -33591,13 +33591,13 @@
         <v>1</v>
       </c>
       <c r="L593" t="n">
-        <v>78231455.95999999</v>
+        <v>50023008.61</v>
       </c>
       <c r="M593" t="n">
-        <v>78231455.95999999</v>
+        <v>50023008.61</v>
       </c>
       <c r="N593" t="n">
-        <v>67381496.97</v>
+        <v>46770710.65</v>
       </c>
     </row>
     <row r="594">
@@ -33606,22 +33606,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2301762 000050/2023</t>
+          <t>2301762 000049/2023</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>9414641</t>
+          <t>9423384</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>DM-006/2024</t>
+          <t>DM-013/2024</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -33647,13 +33647,13 @@
         <v>1</v>
       </c>
       <c r="L594" t="n">
-        <v>7567396.72</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="M594" t="n">
-        <v>7567396.72</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="N594" t="n">
-        <v>5949066.1</v>
+        <v>67381496.97</v>
       </c>
     </row>
     <row r="595">
@@ -33662,22 +33662,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000050/2023</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9414641</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DM-006/2024</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -33703,13 +33703,13 @@
         <v>1</v>
       </c>
       <c r="L595" t="n">
-        <v>57753580.93</v>
+        <v>7567396.72</v>
       </c>
       <c r="M595" t="n">
-        <v>57753580.93</v>
+        <v>7567396.72</v>
       </c>
       <c r="N595" t="n">
-        <v>37310856.76</v>
+        <v>5949066.1</v>
       </c>
     </row>
     <row r="596">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -33779,17 +33779,17 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -33815,13 +33815,13 @@
         <v>1</v>
       </c>
       <c r="L597" t="n">
-        <v>56623238.81</v>
+        <v>57753580.93</v>
       </c>
       <c r="M597" t="n">
-        <v>56623238.81</v>
+        <v>57753580.93</v>
       </c>
       <c r="N597" t="n">
-        <v>37153801.63</v>
+        <v>37310856.76</v>
       </c>
     </row>
     <row r="598">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -33891,17 +33891,17 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -33927,13 +33927,13 @@
         <v>1</v>
       </c>
       <c r="L599" t="n">
-        <v>51505163.41</v>
+        <v>56623238.81</v>
       </c>
       <c r="M599" t="n">
-        <v>51505163.41</v>
+        <v>56623238.81</v>
       </c>
       <c r="N599" t="n">
-        <v>33479427.94</v>
+        <v>37153801.63</v>
       </c>
     </row>
     <row r="600">
@@ -33952,7 +33952,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -34003,17 +34003,17 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>9424447</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>DM-015/2024</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -34039,13 +34039,13 @@
         <v>1</v>
       </c>
       <c r="L601" t="n">
-        <v>50334501.36</v>
+        <v>51505163.41</v>
       </c>
       <c r="M601" t="n">
-        <v>50334501.36</v>
+        <v>51505163.41</v>
       </c>
       <c r="N601" t="n">
-        <v>33230906.95</v>
+        <v>33479427.94</v>
       </c>
     </row>
     <row r="602">
@@ -34059,17 +34059,17 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9424447</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>DM-017/2024</t>
+          <t>DM-015/2024</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -34095,13 +34095,13 @@
         <v>1</v>
       </c>
       <c r="L602" t="n">
-        <v>50026623.29</v>
+        <v>50334501.36</v>
       </c>
       <c r="M602" t="n">
-        <v>50026623.29</v>
+        <v>50334501.36</v>
       </c>
       <c r="N602" t="n">
-        <v>32023158.45</v>
+        <v>33230906.95</v>
       </c>
     </row>
     <row r="603">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-017/2024</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -34171,17 +34171,17 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -34207,13 +34207,13 @@
         <v>1</v>
       </c>
       <c r="L604" t="n">
-        <v>57899353.16</v>
+        <v>50026623.29</v>
       </c>
       <c r="M604" t="n">
-        <v>57899353.16</v>
+        <v>50026623.29</v>
       </c>
       <c r="N604" t="n">
-        <v>34984519.25</v>
+        <v>32023158.45</v>
       </c>
     </row>
     <row r="605">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -34283,17 +34283,17 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -34319,13 +34319,13 @@
         <v>1</v>
       </c>
       <c r="L606" t="n">
-        <v>61509573.94</v>
+        <v>57899353.16</v>
       </c>
       <c r="M606" t="n">
-        <v>61509573.94</v>
+        <v>57899353.16</v>
       </c>
       <c r="N606" t="n">
-        <v>42788655.89</v>
+        <v>34984519.25</v>
       </c>
     </row>
     <row r="607">
@@ -34344,7 +34344,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -34390,54 +34390,54 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2301931 000001/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>9440673</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>AEST-009440673/2024</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F608" t="n">
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>26883</v>
+        <v>1872</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I608" t="n">
-        <v>3502</v>
+        <v>5107</v>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K608" t="n">
         <v>1</v>
       </c>
       <c r="L608" t="n">
-        <v>7699669.8</v>
+        <v>61509573.94</v>
       </c>
       <c r="M608" t="n">
-        <v>7699669.8</v>
+        <v>61509573.94</v>
       </c>
       <c r="N608" t="n">
-        <v>5774752.44</v>
+        <v>42788655.89</v>
       </c>
     </row>
     <row r="609">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>AEST-009440673/2024</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -34502,22 +34502,22 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2301931 000002/2024</t>
+          <t>2301931 000001/2024</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>9441233</t>
+          <t>9440673</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>AEST-9441233/2024</t>
+          <t>PO</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F610" t="n">
@@ -34543,13 +34543,13 @@
         <v>1</v>
       </c>
       <c r="L610" t="n">
-        <v>5947278.86</v>
+        <v>7699669.8</v>
       </c>
       <c r="M610" t="n">
-        <v>0</v>
+        <v>7699669.8</v>
       </c>
       <c r="N610" t="n">
-        <v>0</v>
+        <v>5774752.44</v>
       </c>
     </row>
     <row r="611">
@@ -34588,11 +34588,11 @@
         </is>
       </c>
       <c r="I611" t="n">
-        <v>3973</v>
+        <v>3502</v>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K611" t="n">
@@ -34602,66 +34602,66 @@
         <v>5947278.86</v>
       </c>
       <c r="M611" t="n">
-        <v>5947278.86</v>
+        <v>0</v>
       </c>
       <c r="N611" t="n">
-        <v>5947278.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>1301017 000043/2024</t>
+          <t>2301931 000002/2024</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>9473911</t>
+          <t>9441233</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>9473911/2024</t>
+          <t>AEST-9441233/2024</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
         </is>
       </c>
       <c r="F612" t="n">
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>11207</v>
+        <v>26883</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I612" t="n">
-        <v>3951</v>
+        <v>3973</v>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K612" t="n">
         <v>1</v>
       </c>
       <c r="L612" t="n">
-        <v>6941645.22</v>
+        <v>5947278.86</v>
       </c>
       <c r="M612" t="n">
-        <v>6941645.22</v>
+        <v>5947278.86</v>
       </c>
       <c r="N612" t="n">
-        <v>5206233.96</v>
+        <v>5947278.86</v>
       </c>
     </row>
     <row r="613">
@@ -34689,7 +34689,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G613" t="n">
         <v>11207</v>
@@ -34714,10 +34714,10 @@
         <v>6941645.22</v>
       </c>
       <c r="M613" t="n">
-        <v>0</v>
+        <v>6941645.22</v>
       </c>
       <c r="N613" t="n">
-        <v>0</v>
+        <v>5206233.96</v>
       </c>
     </row>
     <row r="614">
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G614" t="n">
         <v>11207</v>
@@ -34782,54 +34782,54 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>1301017 000043/2024</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9473911</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>9473911/2024</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F615" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G615" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I615" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K615" t="n">
         <v>1</v>
       </c>
       <c r="L615" t="n">
-        <v>25933131.61</v>
+        <v>6941645.22</v>
       </c>
       <c r="M615" t="n">
-        <v>25933131.61</v>
+        <v>0</v>
       </c>
       <c r="N615" t="n">
-        <v>19446841.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
@@ -34838,22 +34838,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2301520 000001/2025</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>9459022</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>DC-9459022/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F616" t="n">
@@ -34879,13 +34879,13 @@
         <v>1</v>
       </c>
       <c r="L616" t="n">
-        <v>13090078.19</v>
+        <v>25933131.61</v>
       </c>
       <c r="M616" t="n">
-        <v>13090078.19</v>
+        <v>25933131.61</v>
       </c>
       <c r="N616" t="n">
-        <v>9817558.640000001</v>
+        <v>19446841.31</v>
       </c>
     </row>
     <row r="617">
@@ -34899,12 +34899,12 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>9459023</t>
+          <t>9459022</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>DC-9459023/2025</t>
+          <t>DC-9459022/2025</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -34935,13 +34935,13 @@
         <v>1</v>
       </c>
       <c r="L617" t="n">
-        <v>39434905.89</v>
+        <v>13090078.19</v>
       </c>
       <c r="M617" t="n">
-        <v>39434905.89</v>
+        <v>13090078.19</v>
       </c>
       <c r="N617" t="n">
-        <v>29576179.41</v>
+        <v>9817558.640000001</v>
       </c>
     </row>
     <row r="618">
@@ -34950,54 +34950,54 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2301520 000002/2025</t>
+          <t>2301520 000001/2025</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>9472756</t>
+          <t>9459023</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DC-9459023/2025</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>ESTEL ENGENHARIA LTDA.</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F618" t="n">
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I618" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K618" t="n">
         <v>1</v>
       </c>
       <c r="L618" t="n">
-        <v>2332947.34</v>
+        <v>39434905.89</v>
       </c>
       <c r="M618" t="n">
-        <v>2332947.34</v>
+        <v>39434905.89</v>
       </c>
       <c r="N618" t="n">
-        <v>1655673.22</v>
+        <v>29576179.41</v>
       </c>
     </row>
     <row r="619">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>DM-001/2022</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -35062,54 +35062,54 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2301520 000004/2025</t>
+          <t>2301520 000002/2025</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>9459021</t>
+          <t>9472756</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>DC-9459021/2025</t>
+          <t>DM-001/2022</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>ESTEL ENGENHARIA LTDA.</t>
         </is>
       </c>
       <c r="F620" t="n">
         <v>1</v>
       </c>
       <c r="G620" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I620" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K620" t="n">
         <v>1</v>
       </c>
       <c r="L620" t="n">
-        <v>40411563.13</v>
+        <v>2332947.34</v>
       </c>
       <c r="M620" t="n">
-        <v>40411563.13</v>
+        <v>2332947.34</v>
       </c>
       <c r="N620" t="n">
-        <v>35900000</v>
+        <v>1655673.22</v>
       </c>
     </row>
     <row r="621">
@@ -35118,22 +35118,22 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2301520 000007/2025</t>
+          <t>2301520 000004/2025</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>9468321</t>
+          <t>9459021</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DC-9459021/2025</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>G S COSTA CONSTRUTORA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F621" t="n">
@@ -35159,13 +35159,13 @@
         <v>1</v>
       </c>
       <c r="L621" t="n">
-        <v>2445446.33</v>
+        <v>40411563.13</v>
       </c>
       <c r="M621" t="n">
-        <v>2445446.33</v>
+        <v>40411563.13</v>
       </c>
       <c r="N621" t="n">
-        <v>2380000</v>
+        <v>35900000</v>
       </c>
     </row>
     <row r="622">
@@ -35174,54 +35174,54 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2301520 000008/2025</t>
+          <t>2301520 000007/2025</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>9472752</t>
+          <t>9468321</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>G S COSTA CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F622" t="n">
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I622" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K622" t="n">
         <v>1</v>
       </c>
       <c r="L622" t="n">
-        <v>9357672.390000001</v>
+        <v>2445446.33</v>
       </c>
       <c r="M622" t="n">
-        <v>9357672.390000001</v>
+        <v>2445446.33</v>
       </c>
       <c r="N622" t="n">
-        <v>7056321.74</v>
+        <v>2380000</v>
       </c>
     </row>
     <row r="623">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>DM-001/2021</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -35286,54 +35286,54 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301520 000008/2025</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9472752</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DM-001/2021</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F624" t="n">
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I624" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K624" t="n">
         <v>1</v>
       </c>
       <c r="L624" t="n">
-        <v>63771944.67</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="M624" t="n">
-        <v>63771944.67</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="N624" t="n">
-        <v>45918998.95</v>
+        <v>7056321.74</v>
       </c>
     </row>
     <row r="625">
@@ -35342,22 +35342,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="F625" t="n">
@@ -35383,13 +35383,13 @@
         <v>1</v>
       </c>
       <c r="L625" t="n">
-        <v>9523161.51</v>
+        <v>63771944.67</v>
       </c>
       <c r="M625" t="n">
-        <v>9523161.51</v>
+        <v>63771944.67</v>
       </c>
       <c r="N625" t="n">
-        <v>9522992.289999999</v>
+        <v>45918998.95</v>
       </c>
     </row>
     <row r="626">
@@ -35398,22 +35398,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>CONSTRUTORA A GASPAR S/A</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F626" t="n">
@@ -35439,13 +35439,13 @@
         <v>1</v>
       </c>
       <c r="L626" t="n">
-        <v>252967153.57</v>
+        <v>9523161.51</v>
       </c>
       <c r="M626" t="n">
-        <v>252967153.57</v>
+        <v>9523161.51</v>
       </c>
       <c r="N626" t="n">
-        <v>207490000</v>
+        <v>9522992.289999999</v>
       </c>
     </row>
     <row r="627">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>DC-012/2023</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -35510,22 +35510,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-012/2023</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>CONSTRUTORA A GASPAR S/A</t>
         </is>
       </c>
       <c r="F628" t="n">
@@ -35551,13 +35551,13 @@
         <v>1</v>
       </c>
       <c r="L628" t="n">
-        <v>7210196.37</v>
+        <v>252967153.57</v>
       </c>
       <c r="M628" t="n">
-        <v>7210196.37</v>
+        <v>252967153.57</v>
       </c>
       <c r="N628" t="n">
-        <v>5978999.99</v>
+        <v>207490000</v>
       </c>
     </row>
     <row r="629">
@@ -35566,22 +35566,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F629" t="n">
@@ -35607,13 +35607,13 @@
         <v>1</v>
       </c>
       <c r="L629" t="n">
-        <v>9049369.99</v>
+        <v>7210196.37</v>
       </c>
       <c r="M629" t="n">
-        <v>9049369.99</v>
+        <v>7210196.37</v>
       </c>
       <c r="N629" t="n">
-        <v>8415499.810000001</v>
+        <v>5978999.99</v>
       </c>
     </row>
     <row r="630">
@@ -35627,12 +35627,12 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>9447761</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -35663,13 +35663,13 @@
         <v>1</v>
       </c>
       <c r="L630" t="n">
-        <v>5032564.85</v>
+        <v>9049369.99</v>
       </c>
       <c r="M630" t="n">
-        <v>5032564.85</v>
+        <v>9049369.99</v>
       </c>
       <c r="N630" t="n">
-        <v>4776981.58</v>
+        <v>8415499.810000001</v>
       </c>
     </row>
     <row r="631">
@@ -35678,54 +35678,54 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9447761</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F631" t="n">
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I631" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K631" t="n">
         <v>1</v>
       </c>
       <c r="L631" t="n">
-        <v>4575396.26</v>
+        <v>5032564.85</v>
       </c>
       <c r="M631" t="n">
-        <v>4575396.26</v>
+        <v>5032564.85</v>
       </c>
       <c r="N631" t="n">
-        <v>3187539.16</v>
+        <v>4776981.58</v>
       </c>
     </row>
     <row r="632">
@@ -35734,17 +35734,17 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -35775,13 +35775,13 @@
         <v>1</v>
       </c>
       <c r="L632" t="n">
-        <v>3499878.79</v>
+        <v>4575396.26</v>
       </c>
       <c r="M632" t="n">
-        <v>3499878.79</v>
+        <v>4575396.26</v>
       </c>
       <c r="N632" t="n">
-        <v>2624909.09</v>
+        <v>3187539.16</v>
       </c>
     </row>
     <row r="633">
@@ -35790,54 +35790,54 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2301520 000024/2024</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>9458476</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>DC-9458476/2025</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F633" t="n">
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I633" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K633" t="n">
         <v>1</v>
       </c>
       <c r="L633" t="n">
-        <v>104863231.67</v>
+        <v>3499878.79</v>
       </c>
       <c r="M633" t="n">
-        <v>104863231.67</v>
+        <v>3499878.79</v>
       </c>
       <c r="N633" t="n">
-        <v>78647423.75</v>
+        <v>2624909.09</v>
       </c>
     </row>
     <row r="634">
@@ -35846,54 +35846,54 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000024/2024</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9458476</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9458476/2025</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F634" t="n">
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I634" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K634" t="n">
         <v>1</v>
       </c>
       <c r="L634" t="n">
-        <v>5765714.24</v>
+        <v>104863231.67</v>
       </c>
       <c r="M634" t="n">
-        <v>5765714.24</v>
+        <v>104863231.67</v>
       </c>
       <c r="N634" t="n">
-        <v>4324285.68</v>
+        <v>78647423.75</v>
       </c>
     </row>
     <row r="635">
@@ -35902,54 +35902,54 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>CONSTRUTORA MARINS LTDA</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F635" t="n">
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I635" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K635" t="n">
         <v>1</v>
       </c>
       <c r="L635" t="n">
-        <v>4553972.46</v>
+        <v>5765714.24</v>
       </c>
       <c r="M635" t="n">
-        <v>4553972.46</v>
+        <v>5765714.24</v>
       </c>
       <c r="N635" t="n">
-        <v>4553800</v>
+        <v>4324285.68</v>
       </c>
     </row>
     <row r="636">
@@ -35958,54 +35958,54 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2301520 000027/2023</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
+          <t>CONSTRUTORA MARINS LTDA</t>
         </is>
       </c>
       <c r="F636" t="n">
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I636" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K636" t="n">
         <v>1</v>
       </c>
       <c r="L636" t="n">
-        <v>10169679.88</v>
+        <v>4553972.46</v>
       </c>
       <c r="M636" t="n">
-        <v>10169679.88</v>
+        <v>4553972.46</v>
       </c>
       <c r="N636" t="n">
-        <v>9659997.08</v>
+        <v>4553800</v>
       </c>
     </row>
     <row r="637">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -36070,54 +36070,54 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2301520 000027/2024</t>
+          <t>2301520 000027/2023</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>9458861</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>DC-9458861/2025</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
         </is>
       </c>
       <c r="F638" t="n">
         <v>1</v>
       </c>
       <c r="G638" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I638" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K638" t="n">
         <v>1</v>
       </c>
       <c r="L638" t="n">
-        <v>32377230.57</v>
+        <v>10169679.88</v>
       </c>
       <c r="M638" t="n">
-        <v>32377230.57</v>
+        <v>10169679.88</v>
       </c>
       <c r="N638" t="n">
-        <v>24981452.5</v>
+        <v>9659997.08</v>
       </c>
     </row>
     <row r="639">
@@ -36126,22 +36126,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2301520 000028/2025</t>
+          <t>2301520 000027/2024</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>9491013</t>
+          <t>9458861</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DC-9458861/2025</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>VEREDA ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -36167,13 +36167,13 @@
         <v>1</v>
       </c>
       <c r="L639" t="n">
-        <v>22364155.09</v>
+        <v>32377230.57</v>
       </c>
       <c r="M639" t="n">
-        <v>22364155.09</v>
+        <v>32377230.57</v>
       </c>
       <c r="N639" t="n">
-        <v>20125000</v>
+        <v>24981452.5</v>
       </c>
     </row>
     <row r="640">
@@ -36182,22 +36182,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2301520 000029/2025</t>
+          <t>2301520 000028/2025</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>9478759</t>
+          <t>9491013</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
+          <t>VEREDA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -36223,13 +36223,13 @@
         <v>1</v>
       </c>
       <c r="L640" t="n">
-        <v>17183580.33</v>
+        <v>22364155.09</v>
       </c>
       <c r="M640" t="n">
-        <v>17183580.33</v>
+        <v>22364155.09</v>
       </c>
       <c r="N640" t="n">
-        <v>14619000</v>
+        <v>20125000</v>
       </c>
     </row>
     <row r="641">
@@ -36238,54 +36238,54 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2301520 000031/2025</t>
+          <t>2301520 000029/2025</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>9481581</t>
+          <t>9478759</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>DC-9481581/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
         </is>
       </c>
       <c r="F641" t="n">
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I641" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K641" t="n">
         <v>1</v>
       </c>
       <c r="L641" t="n">
-        <v>29147315.1</v>
+        <v>17183580.33</v>
       </c>
       <c r="M641" t="n">
-        <v>29147315.1</v>
+        <v>17183580.33</v>
       </c>
       <c r="N641" t="n">
-        <v>21860486.4</v>
+        <v>14619000</v>
       </c>
     </row>
     <row r="642">
@@ -36313,7 +36313,7 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G642" t="n">
         <v>10774</v>
@@ -36338,10 +36338,10 @@
         <v>29147315.1</v>
       </c>
       <c r="M642" t="n">
-        <v>0</v>
+        <v>29147315.1</v>
       </c>
       <c r="N642" t="n">
-        <v>0</v>
+        <v>21860486.4</v>
       </c>
     </row>
     <row r="643">
@@ -36350,54 +36350,54 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301520 000031/2025</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9481581</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G643" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I643" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K643" t="n">
         <v>1</v>
       </c>
       <c r="L643" t="n">
-        <v>65309420.72</v>
+        <v>29147315.1</v>
       </c>
       <c r="M643" t="n">
-        <v>65309420.72</v>
+        <v>0</v>
       </c>
       <c r="N643" t="n">
-        <v>57467603.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="644">
@@ -36406,22 +36406,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -36447,13 +36447,13 @@
         <v>1</v>
       </c>
       <c r="L644" t="n">
-        <v>74235570.89</v>
+        <v>65309420.72</v>
       </c>
       <c r="M644" t="n">
-        <v>74235570.89</v>
+        <v>65309420.72</v>
       </c>
       <c r="N644" t="n">
-        <v>59890000</v>
+        <v>57467603.75</v>
       </c>
     </row>
     <row r="645">
@@ -36462,54 +36462,54 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2301601 000002/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>9470883</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>DPEI-9470883</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F645" t="n">
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>10693</v>
+        <v>1740</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I645" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K645" t="n">
         <v>1</v>
       </c>
       <c r="L645" t="n">
-        <v>34605227.68</v>
+        <v>74235570.89</v>
       </c>
       <c r="M645" t="n">
-        <v>34605227.68</v>
+        <v>74235570.89</v>
       </c>
       <c r="N645" t="n">
-        <v>25953920.64</v>
+        <v>59890000</v>
       </c>
     </row>
     <row r="646">
@@ -36518,33 +36518,33 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2301601 000003/2025</t>
+          <t>2301601 000002/2025</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>9470151</t>
+          <t>9470883</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DPEI-9470883</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F646" t="n">
         <v>1</v>
       </c>
       <c r="G646" t="n">
-        <v>46850</v>
+        <v>10693</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
         </is>
       </c>
       <c r="I646" t="n">
@@ -36559,13 +36559,13 @@
         <v>1</v>
       </c>
       <c r="L646" t="n">
-        <v>28087551.11</v>
+        <v>34605227.68</v>
       </c>
       <c r="M646" t="n">
-        <v>28087551.11</v>
+        <v>34605227.68</v>
       </c>
       <c r="N646" t="n">
-        <v>22458906.7</v>
+        <v>25953920.64</v>
       </c>
     </row>
     <row r="647">
@@ -36574,54 +36574,54 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301601 000003/2025</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>9447985</t>
+          <t>9470151</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>DPEI-9447985</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F647" t="n">
         <v>1</v>
       </c>
       <c r="G647" t="n">
-        <v>23159</v>
+        <v>46850</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
         </is>
       </c>
       <c r="I647" t="n">
-        <v>3981</v>
+        <v>3951</v>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K647" t="n">
         <v>1</v>
       </c>
       <c r="L647" t="n">
-        <v>6361273.94</v>
+        <v>28087551.11</v>
       </c>
       <c r="M647" t="n">
-        <v>6361273.94</v>
+        <v>28087551.11</v>
       </c>
       <c r="N647" t="n">
-        <v>2540551.02</v>
+        <v>22458906.7</v>
       </c>
     </row>
     <row r="648">
@@ -36630,50 +36630,54 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2301601 000004/2025</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>9478110</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr"/>
+          <t>9447985</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>DPEI-9447985</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>FUNDACAO GETULIO VARGAS</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F648" t="n">
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>26883</v>
+        <v>23159</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I648" t="n">
-        <v>3502</v>
+        <v>3981</v>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K648" t="n">
         <v>1</v>
       </c>
       <c r="L648" t="n">
-        <v>22278613.12</v>
+        <v>6361273.94</v>
       </c>
       <c r="M648" t="n">
-        <v>22278613.12</v>
+        <v>6361273.94</v>
       </c>
       <c r="N648" t="n">
-        <v>22278613.12</v>
+        <v>2540551.02</v>
       </c>
     </row>
     <row r="649">
@@ -36682,22 +36686,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301601 000004/2025</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>9478941</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>DPEI-9478941/2025</t>
-        </is>
-      </c>
+          <t>9478110</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>FUNDACAO GETULIO VARGAS</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -36723,13 +36723,13 @@
         <v>1</v>
       </c>
       <c r="L649" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
       <c r="M649" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
       <c r="N649" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
     </row>
     <row r="650">
@@ -36738,54 +36738,54 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2301617 000002/2025</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>9461425</t>
+          <t>9478941</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>AMA-9461425/2025</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="F650" t="n">
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>23167</v>
+        <v>26883</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I650" t="n">
-        <v>3999</v>
+        <v>3502</v>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K650" t="n">
         <v>1</v>
       </c>
       <c r="L650" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
       <c r="M650" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
       <c r="N650" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
     </row>
     <row r="651">
@@ -36835,13 +36835,13 @@
         <v>1</v>
       </c>
       <c r="L651" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
       <c r="M651" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
       <c r="N651" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
     </row>
     <row r="652">
@@ -36850,22 +36850,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2301617 000004/2024</t>
+          <t>2301617 000002/2025</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>9447965</t>
+          <t>9461425</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>AMA-9447965/2025</t>
+          <t>AMA-9461425/2025</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F652" t="n">
@@ -36891,13 +36891,13 @@
         <v>1</v>
       </c>
       <c r="L652" t="n">
-        <v>965839.63</v>
+        <v>38863.58</v>
       </c>
       <c r="M652" t="n">
-        <v>965839.63</v>
+        <v>38863.58</v>
       </c>
       <c r="N652" t="n">
-        <v>924684.42</v>
+        <v>38863.58</v>
       </c>
     </row>
     <row r="653">
@@ -36906,17 +36906,17 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2301617 000005/2024</t>
+          <t>2301617 000004/2024</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>9458828</t>
+          <t>9447965</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>AMA-9458828/2025</t>
+          <t>AMA-9447965/2025</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -36947,13 +36947,13 @@
         <v>1</v>
       </c>
       <c r="L653" t="n">
-        <v>839153.24</v>
+        <v>965839.63</v>
       </c>
       <c r="M653" t="n">
-        <v>839153.24</v>
+        <v>965839.63</v>
       </c>
       <c r="N653" t="n">
-        <v>803371.39</v>
+        <v>924684.42</v>
       </c>
     </row>
     <row r="654">
@@ -36962,54 +36962,54 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301617 000005/2024</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9458828</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>AMA-9458828/2025</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F654" t="n">
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>1872</v>
+        <v>23167</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I654" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K654" t="n">
         <v>1</v>
       </c>
       <c r="L654" t="n">
-        <v>75462448.56</v>
+        <v>839153.24</v>
       </c>
       <c r="M654" t="n">
-        <v>75462448.56</v>
+        <v>839153.24</v>
       </c>
       <c r="N654" t="n">
-        <v>53573999.99</v>
+        <v>803371.39</v>
       </c>
     </row>
     <row r="655">
@@ -37023,17 +37023,17 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -37059,13 +37059,13 @@
         <v>1</v>
       </c>
       <c r="L655" t="n">
-        <v>74549476.59</v>
+        <v>75462448.56</v>
       </c>
       <c r="M655" t="n">
-        <v>74549476.59</v>
+        <v>75462448.56</v>
       </c>
       <c r="N655" t="n">
-        <v>49093539.45</v>
+        <v>53573999.99</v>
       </c>
     </row>
     <row r="656">
@@ -37079,17 +37079,17 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -37115,13 +37115,13 @@
         <v>1</v>
       </c>
       <c r="L656" t="n">
-        <v>71047185.15000001</v>
+        <v>74549476.59</v>
       </c>
       <c r="M656" t="n">
-        <v>71047185.15000001</v>
+        <v>74549476.59</v>
       </c>
       <c r="N656" t="n">
-        <v>50960749.38</v>
+        <v>49093539.45</v>
       </c>
     </row>
     <row r="657">
@@ -37135,17 +37135,17 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="F657" t="n">
@@ -37171,13 +37171,13 @@
         <v>1</v>
       </c>
       <c r="L657" t="n">
-        <v>71318172.81999999</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="M657" t="n">
-        <v>71318172.81999999</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="N657" t="n">
-        <v>44573000</v>
+        <v>50960749.38</v>
       </c>
     </row>
     <row r="658">
@@ -37191,17 +37191,17 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>9471879</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -37227,13 +37227,13 @@
         <v>1</v>
       </c>
       <c r="L658" t="n">
-        <v>80365266.31999999</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="M658" t="n">
-        <v>80365266.31999999</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="N658" t="n">
-        <v>53241874.38</v>
+        <v>44573000</v>
       </c>
     </row>
     <row r="659">
@@ -37247,17 +37247,17 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -37283,13 +37283,13 @@
         <v>1</v>
       </c>
       <c r="L659" t="n">
-        <v>76047809.47</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="M659" t="n">
-        <v>76047809.47</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="N659" t="n">
-        <v>51814575.44</v>
+        <v>53241874.38</v>
       </c>
     </row>
     <row r="660">
@@ -37303,17 +37303,17 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -37339,13 +37339,13 @@
         <v>1</v>
       </c>
       <c r="L660" t="n">
-        <v>76234321.51000001</v>
+        <v>76047809.47</v>
       </c>
       <c r="M660" t="n">
-        <v>76234321.51000001</v>
+        <v>76047809.47</v>
       </c>
       <c r="N660" t="n">
-        <v>53358800</v>
+        <v>51814575.44</v>
       </c>
     </row>
     <row r="661">
@@ -37359,17 +37359,17 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -37395,13 +37395,13 @@
         <v>1</v>
       </c>
       <c r="L661" t="n">
-        <v>88896704.79000001</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="M661" t="n">
-        <v>88896704.79000001</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="N661" t="n">
-        <v>59299394.97</v>
+        <v>53358800</v>
       </c>
     </row>
     <row r="662">
@@ -37410,22 +37410,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2301762 000004/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>9473312</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -37451,13 +37451,13 @@
         <v>1</v>
       </c>
       <c r="L662" t="n">
-        <v>8322333.63</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="M662" t="n">
-        <v>8322333.63</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="N662" t="n">
-        <v>7074995.71</v>
+        <v>59299394.97</v>
       </c>
     </row>
     <row r="663">
@@ -37466,17 +37466,17 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2301762 000005/2025</t>
+          <t>2301762 000004/2025</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>9474704</t>
+          <t>9473312</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -37507,13 +37507,13 @@
         <v>1</v>
       </c>
       <c r="L663" t="n">
-        <v>9663464.630000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="M663" t="n">
-        <v>9663464.630000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="N663" t="n">
-        <v>7710000</v>
+        <v>7074995.71</v>
       </c>
     </row>
     <row r="664">
@@ -37522,22 +37522,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2301762 000016/2025</t>
+          <t>2301762 000005/2025</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>9485592</t>
+          <t>9474704</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>DM-9485592/2025</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -37563,13 +37563,13 @@
         <v>1</v>
       </c>
       <c r="L664" t="n">
-        <v>13962359.26</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="M664" t="n">
-        <v>13962359.26</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="N664" t="n">
-        <v>10929975.56</v>
+        <v>7710000</v>
       </c>
     </row>
     <row r="665">
@@ -37578,22 +37578,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2301762 000017/2024</t>
+          <t>2301762 000016/2025</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>9447456</t>
+          <t>9485592</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DM-9485592/2025</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -37619,13 +37619,13 @@
         <v>1</v>
       </c>
       <c r="L665" t="n">
-        <v>6557067.25</v>
+        <v>13962359.26</v>
       </c>
       <c r="M665" t="n">
-        <v>6557067.25</v>
+        <v>13962359.26</v>
       </c>
       <c r="N665" t="n">
-        <v>4917800.43</v>
+        <v>10929975.56</v>
       </c>
     </row>
     <row r="666">
@@ -37634,22 +37634,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2301762 000017/2025</t>
+          <t>2301762 000017/2024</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>9485591</t>
+          <t>9447456</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>DM-9485591/2025</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -37675,13 +37675,13 @@
         <v>1</v>
       </c>
       <c r="L666" t="n">
-        <v>8331047.13</v>
+        <v>6557067.25</v>
       </c>
       <c r="M666" t="n">
-        <v>8331047.13</v>
+        <v>6557067.25</v>
       </c>
       <c r="N666" t="n">
-        <v>6199729.76</v>
+        <v>4917800.43</v>
       </c>
     </row>
     <row r="667">
@@ -37690,22 +37690,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2301762 000018/2024</t>
+          <t>2301762 000017/2025</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>9454417</t>
+          <t>9485591</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>DM-9454417/2025</t>
+          <t>DM-9485591/2025</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -37731,13 +37731,13 @@
         <v>1</v>
       </c>
       <c r="L667" t="n">
-        <v>38329183.15</v>
+        <v>8331047.13</v>
       </c>
       <c r="M667" t="n">
-        <v>38329183.15</v>
+        <v>8331047.13</v>
       </c>
       <c r="N667" t="n">
-        <v>28746887.36</v>
+        <v>6199729.76</v>
       </c>
     </row>
     <row r="668">
@@ -37746,22 +37746,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2301762 000019/2024</t>
+          <t>2301762 000018/2024</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>9452477</t>
+          <t>9454417</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>DM-9454417/2025</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -37787,13 +37787,13 @@
         <v>1</v>
       </c>
       <c r="L668" t="n">
-        <v>52446095.99</v>
+        <v>38329183.15</v>
       </c>
       <c r="M668" t="n">
-        <v>52446095.99</v>
+        <v>38329183.15</v>
       </c>
       <c r="N668" t="n">
-        <v>39334571.99</v>
+        <v>28746887.36</v>
       </c>
     </row>
     <row r="669">
@@ -37802,22 +37802,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301762 000019/2024</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9452477</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -37843,13 +37843,13 @@
         <v>1</v>
       </c>
       <c r="L669" t="n">
-        <v>59309539.93</v>
+        <v>52446095.99</v>
       </c>
       <c r="M669" t="n">
-        <v>59309539.93</v>
+        <v>52446095.99</v>
       </c>
       <c r="N669" t="n">
-        <v>44482154.94</v>
+        <v>39334571.99</v>
       </c>
     </row>
     <row r="670">
@@ -37858,22 +37858,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -37899,13 +37899,13 @@
         <v>1</v>
       </c>
       <c r="L670" t="n">
-        <v>9479564.210000001</v>
+        <v>59309539.93</v>
       </c>
       <c r="M670" t="n">
-        <v>9479564.210000001</v>
+        <v>59309539.93</v>
       </c>
       <c r="N670" t="n">
-        <v>7109673.15</v>
+        <v>44482154.94</v>
       </c>
     </row>
     <row r="671">
@@ -37914,22 +37914,22 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -37955,13 +37955,13 @@
         <v>1</v>
       </c>
       <c r="L671" t="n">
-        <v>60200606.24</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="M671" t="n">
-        <v>60200606.24</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="N671" t="n">
-        <v>41984578.11</v>
+        <v>7109673.15</v>
       </c>
     </row>
     <row r="672">
@@ -37970,54 +37970,54 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F672" t="n">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>11207</v>
+        <v>1872</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I672" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K672" t="n">
         <v>1</v>
       </c>
       <c r="L672" t="n">
-        <v>25269915.6</v>
+        <v>60200606.24</v>
       </c>
       <c r="M672" t="n">
-        <v>25269915.6</v>
+        <v>60200606.24</v>
       </c>
       <c r="N672" t="n">
-        <v>23434999.8</v>
+        <v>41984578.11</v>
       </c>
     </row>
     <row r="673">
@@ -38031,49 +38031,49 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F673" t="n">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>66419</v>
+        <v>11207</v>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I673" t="n">
-        <v>3971</v>
+        <v>3951</v>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K673" t="n">
         <v>1</v>
       </c>
       <c r="L673" t="n">
-        <v>87218202.05</v>
+        <v>25269915.6</v>
       </c>
       <c r="M673" t="n">
-        <v>87218202.05</v>
+        <v>25269915.6</v>
       </c>
       <c r="N673" t="n">
-        <v>77898894.3</v>
+        <v>23434999.8</v>
       </c>
     </row>
     <row r="674">
@@ -38092,7 +38092,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO009482014/2025</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -38143,17 +38143,17 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -38179,13 +38179,13 @@
         <v>1</v>
       </c>
       <c r="L675" t="n">
-        <v>79690903.56</v>
+        <v>87218202.05</v>
       </c>
       <c r="M675" t="n">
-        <v>79690903.56</v>
+        <v>87218202.05</v>
       </c>
       <c r="N675" t="n">
-        <v>47349998.43</v>
+        <v>77898894.3</v>
       </c>
     </row>
     <row r="676">
@@ -38199,17 +38199,17 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -38235,13 +38235,13 @@
         <v>1</v>
       </c>
       <c r="L676" t="n">
-        <v>73884529.66</v>
+        <v>79690903.56</v>
       </c>
       <c r="M676" t="n">
-        <v>73884529.66</v>
+        <v>79690903.56</v>
       </c>
       <c r="N676" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="677">
@@ -38255,17 +38255,17 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -38291,13 +38291,13 @@
         <v>1</v>
       </c>
       <c r="L677" t="n">
-        <v>75334510.38</v>
+        <v>73884529.66</v>
       </c>
       <c r="M677" t="n">
-        <v>75334510.38</v>
+        <v>73884529.66</v>
       </c>
       <c r="N677" t="n">
-        <v>45188997.86</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="678">
@@ -38311,17 +38311,17 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -38347,13 +38347,13 @@
         <v>1</v>
       </c>
       <c r="L678" t="n">
-        <v>65055206.84</v>
+        <v>73884529.66</v>
       </c>
       <c r="M678" t="n">
-        <v>65055206.84</v>
+        <v>73884529.66</v>
       </c>
       <c r="N678" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="679">
@@ -38362,54 +38362,54 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>9468567</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>AEST-9468567/2025</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="F679" t="n">
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>26883</v>
+        <v>66419</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I679" t="n">
-        <v>3502</v>
+        <v>3971</v>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K679" t="n">
         <v>1</v>
       </c>
       <c r="L679" t="n">
-        <v>12267717.16</v>
+        <v>75334510.38</v>
       </c>
       <c r="M679" t="n">
-        <v>12267717.16</v>
+        <v>75334510.38</v>
       </c>
       <c r="N679" t="n">
-        <v>9200787.869999999</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="680">
@@ -38418,54 +38418,54 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="F680" t="n">
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>26883</v>
+        <v>66419</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I680" t="n">
-        <v>3502</v>
+        <v>3971</v>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K680" t="n">
         <v>1</v>
       </c>
       <c r="L680" t="n">
-        <v>12291296.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="M680" t="n">
-        <v>12291296.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="N680" t="n">
-        <v>9218472.49</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="681">
@@ -38479,17 +38479,17 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9468567</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>AEST-9468567/2025</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -38515,13 +38515,13 @@
         <v>1</v>
       </c>
       <c r="L681" t="n">
-        <v>12197245.67</v>
+        <v>12267717.16</v>
       </c>
       <c r="M681" t="n">
-        <v>12197245.67</v>
+        <v>12267717.16</v>
       </c>
       <c r="N681" t="n">
-        <v>9147934.25</v>
+        <v>9200787.869999999</v>
       </c>
     </row>
     <row r="682">
@@ -38535,17 +38535,17 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>9469794</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -38571,13 +38571,13 @@
         <v>1</v>
       </c>
       <c r="L682" t="n">
-        <v>12379211.81</v>
+        <v>12291296.66</v>
       </c>
       <c r="M682" t="n">
-        <v>12379211.81</v>
+        <v>12291296.66</v>
       </c>
       <c r="N682" t="n">
-        <v>9284408.859999999</v>
+        <v>9218472.49</v>
       </c>
     </row>
     <row r="683">
@@ -38591,17 +38591,17 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>9470136</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>AEST-9470136/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -38627,125 +38627,125 @@
         <v>1</v>
       </c>
       <c r="L683" t="n">
-        <v>12547127.86</v>
+        <v>12197245.67</v>
       </c>
       <c r="M683" t="n">
-        <v>12547127.86</v>
+        <v>12197245.67</v>
       </c>
       <c r="N683" t="n">
-        <v>9410345.9</v>
+        <v>9147934.25</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9469794</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>PROCEC ENGENHARIA S.A</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F684" t="n">
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>1740</v>
+        <v>26883</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I684" t="n">
-        <v>5107</v>
+        <v>3502</v>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K684" t="n">
         <v>1</v>
       </c>
       <c r="L684" t="n">
-        <v>5887057.98</v>
+        <v>12379211.81</v>
       </c>
       <c r="M684" t="n">
-        <v>5887057.98</v>
+        <v>12379211.81</v>
       </c>
       <c r="N684" t="n">
-        <v>5658828.94</v>
+        <v>9284408.859999999</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9470136</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AEST-9470136/2025</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>OPACO ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="F685" t="n">
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>1740</v>
+        <v>26883</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I685" t="n">
-        <v>5107</v>
+        <v>3502</v>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K685" t="n">
         <v>1</v>
       </c>
       <c r="L685" t="n">
-        <v>28204745.51</v>
+        <v>12547127.86</v>
       </c>
       <c r="M685" t="n">
-        <v>28204745.51</v>
+        <v>12547127.86</v>
       </c>
       <c r="N685" t="n">
-        <v>28204745.51</v>
+        <v>9410345.9</v>
       </c>
     </row>
     <row r="686">
@@ -38754,22 +38754,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
+          <t>PROCEC ENGENHARIA S.A</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -38795,13 +38795,13 @@
         <v>1</v>
       </c>
       <c r="L686" t="n">
-        <v>4383662.29</v>
+        <v>5887057.98</v>
       </c>
       <c r="M686" t="n">
-        <v>4383662.29</v>
+        <v>5887057.98</v>
       </c>
       <c r="N686" t="n">
-        <v>3700000</v>
+        <v>5658828.94</v>
       </c>
     </row>
     <row r="687">
@@ -38810,18 +38810,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr"/>
+          <t>9507997</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>OPACO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -38844,16 +38848,16 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L687" t="n">
-        <v>19733859.27</v>
+        <v>28204745.51</v>
       </c>
       <c r="M687" t="n">
-        <v>19733859.26</v>
+        <v>28204745.51</v>
       </c>
       <c r="N687" t="n">
-        <v>16179998.72</v>
+        <v>28204745.51</v>
       </c>
     </row>
     <row r="688">
@@ -38862,18 +38866,22 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>9515457</t>
-        </is>
-      </c>
-      <c r="D688" t="inlineStr"/>
+          <t>9497471</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -38896,16 +38904,16 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L688" t="n">
-        <v>120767701.47</v>
+        <v>4383662.29</v>
       </c>
       <c r="M688" t="n">
-        <v>120767701.47</v>
+        <v>4383662.29</v>
       </c>
       <c r="N688" t="n">
-        <v>87996201.20999999</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="689">
@@ -38914,18 +38922,22 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>9518140</t>
-        </is>
-      </c>
-      <c r="D689" t="inlineStr"/>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SINARCO LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F689" t="n">
@@ -38948,16 +38960,16 @@
         </is>
       </c>
       <c r="K689" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L689" t="n">
-        <v>83862492.89</v>
+        <v>19733859.27</v>
       </c>
       <c r="M689" t="n">
-        <v>83862492.89</v>
+        <v>19733859.26</v>
       </c>
       <c r="N689" t="n">
-        <v>77916642.14</v>
+        <v>16179998.72</v>
       </c>
     </row>
     <row r="690">
@@ -38966,17 +38978,17 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -39004,16 +39016,16 @@
         </is>
       </c>
       <c r="K690" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L690" t="n">
-        <v>2962697.76</v>
+        <v>120767701.47</v>
       </c>
       <c r="M690" t="n">
-        <v>2962697.76</v>
+        <v>120767701.47</v>
       </c>
       <c r="N690" t="n">
-        <v>2962697.76</v>
+        <v>87996201.20999999</v>
       </c>
     </row>
     <row r="691">
@@ -39022,15 +39034,19 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>9518942</t>
-        </is>
-      </c>
-      <c r="D691" t="inlineStr"/>
+          <t>9518140</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
           <t>CONSTRUTORA SINARCO LTDA</t>
@@ -39059,13 +39075,13 @@
         <v>1</v>
       </c>
       <c r="L691" t="n">
-        <v>83450845.04000001</v>
+        <v>83862492.89</v>
       </c>
       <c r="M691" t="n">
-        <v>83450845.04000001</v>
+        <v>83862492.89</v>
       </c>
       <c r="N691" t="n">
-        <v>61779996.11</v>
+        <v>77916642.14</v>
       </c>
     </row>
     <row r="692">
@@ -39074,18 +39090,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2301520 000017/2026</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>9519017</t>
-        </is>
-      </c>
-      <c r="D692" t="inlineStr"/>
+          <t>9498942</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>DC-011R/2024</t>
+        </is>
+      </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -39111,13 +39131,13 @@
         <v>1</v>
       </c>
       <c r="L692" t="n">
-        <v>6602550.32</v>
+        <v>2962697.76</v>
       </c>
       <c r="M692" t="n">
-        <v>6602550.32</v>
+        <v>2962697.76</v>
       </c>
       <c r="N692" t="n">
-        <v>5995000</v>
+        <v>2962697.76</v>
       </c>
     </row>
     <row r="693">
@@ -39126,18 +39146,22 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>9519295</t>
-        </is>
-      </c>
-      <c r="D693" t="inlineStr"/>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CONSTRUTORA SINARCO LTDA</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -39163,13 +39187,13 @@
         <v>1</v>
       </c>
       <c r="L693" t="n">
-        <v>37610115.71</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="M693" t="n">
-        <v>37610115.71</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="N693" t="n">
-        <v>34487308.95</v>
+        <v>61779996.11</v>
       </c>
     </row>
     <row r="694">
@@ -39178,18 +39202,22 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301520 000017/2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>9519020</t>
-        </is>
-      </c>
-      <c r="D694" t="inlineStr"/>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>DC-9519017/2026</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F694" t="n">
@@ -39215,13 +39243,13 @@
         <v>1</v>
       </c>
       <c r="L694" t="n">
-        <v>8481152.01</v>
+        <v>6602550.32</v>
       </c>
       <c r="M694" t="n">
-        <v>8481152.01</v>
+        <v>6602550.32</v>
       </c>
       <c r="N694" t="n">
-        <v>7088404.99</v>
+        <v>5995000</v>
       </c>
     </row>
     <row r="695">
@@ -39230,22 +39258,22 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F695" t="n">
@@ -39271,13 +39299,13 @@
         <v>1</v>
       </c>
       <c r="L695" t="n">
-        <v>15970367.44</v>
+        <v>37610115.71</v>
       </c>
       <c r="M695" t="n">
-        <v>15970367.44</v>
+        <v>37610115.71</v>
       </c>
       <c r="N695" t="n">
-        <v>12246077.75</v>
+        <v>34487308.95</v>
       </c>
     </row>
     <row r="696">
@@ -39286,54 +39314,54 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F696" t="n">
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I696" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K696" t="n">
         <v>1</v>
       </c>
       <c r="L696" t="n">
-        <v>7420078.73</v>
+        <v>37610115.71</v>
       </c>
       <c r="M696" t="n">
-        <v>7420078.73</v>
+        <v>37610115.71</v>
       </c>
       <c r="N696" t="n">
-        <v>6677404.33</v>
+        <v>34487308.95</v>
       </c>
     </row>
     <row r="697">
@@ -39342,54 +39370,54 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F697" t="n">
         <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I697" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K697" t="n">
         <v>1</v>
       </c>
       <c r="L697" t="n">
-        <v>3563439</v>
+        <v>8481152.01</v>
       </c>
       <c r="M697" t="n">
-        <v>3563439</v>
+        <v>8481152.01</v>
       </c>
       <c r="N697" t="n">
-        <v>3028048.96</v>
+        <v>7088404.99</v>
       </c>
     </row>
     <row r="698">
@@ -39398,22 +39426,22 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CONTORNO LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F698" t="n">
@@ -39439,13 +39467,13 @@
         <v>1</v>
       </c>
       <c r="L698" t="n">
-        <v>44004328.59</v>
+        <v>15970367.44</v>
       </c>
       <c r="M698" t="n">
-        <v>44004328.59</v>
+        <v>15970367.44</v>
       </c>
       <c r="N698" t="n">
-        <v>37600000</v>
+        <v>12246077.75</v>
       </c>
     </row>
     <row r="699">
@@ -39454,54 +39482,54 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F699" t="n">
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I699" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K699" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L699" t="n">
-        <v>11144418.23</v>
+        <v>7420078.73</v>
       </c>
       <c r="M699" t="n">
-        <v>11144418.22</v>
+        <v>7420078.73</v>
       </c>
       <c r="N699" t="n">
-        <v>9814000</v>
+        <v>6677404.33</v>
       </c>
     </row>
     <row r="700">
@@ -39510,50 +39538,54 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2301520 000037/2026</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>9519595</t>
-        </is>
-      </c>
-      <c r="D700" t="inlineStr"/>
+          <t>9492715</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>DC-9492715/2025</t>
+        </is>
+      </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>L.M. EMPREENDIMENTOS E CONSULTORIA LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F700" t="n">
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I700" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K700" t="n">
         <v>1</v>
       </c>
       <c r="L700" t="n">
-        <v>79427050.02</v>
+        <v>3563439</v>
       </c>
       <c r="M700" t="n">
-        <v>79427050.02</v>
+        <v>3563439</v>
       </c>
       <c r="N700" t="n">
-        <v>69497864.40000001</v>
+        <v>3028048.96</v>
       </c>
     </row>
     <row r="701">
@@ -39562,18 +39594,22 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>9519740</t>
-        </is>
-      </c>
-      <c r="D701" t="inlineStr"/>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>DIFFERENCIAL ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CONTORNO LTDA</t>
         </is>
       </c>
       <c r="F701" t="n">
@@ -39599,13 +39635,13 @@
         <v>1</v>
       </c>
       <c r="L701" t="n">
-        <v>33864867.02</v>
+        <v>44004328.59</v>
       </c>
       <c r="M701" t="n">
-        <v>33864867.02</v>
+        <v>44004328.59</v>
       </c>
       <c r="N701" t="n">
-        <v>27896726.26</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="702">
@@ -39614,50 +39650,54 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>9498666</t>
-        </is>
-      </c>
-      <c r="D702" t="inlineStr"/>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F702" t="n">
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I702" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K702" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L702" t="n">
-        <v>32765091.84</v>
+        <v>11144418.23</v>
       </c>
       <c r="M702" t="n">
-        <v>32765091.84</v>
+        <v>11144418.22</v>
       </c>
       <c r="N702" t="n">
-        <v>23052682.68</v>
+        <v>9814000</v>
       </c>
     </row>
     <row r="703">
@@ -39666,50 +39706,50 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>L.M. EMPREENDIMENTOS E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F703" t="n">
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I703" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K703" t="n">
         <v>1</v>
       </c>
       <c r="L703" t="n">
-        <v>6323844.01</v>
+        <v>79427050.02</v>
       </c>
       <c r="M703" t="n">
-        <v>6323844.01</v>
+        <v>79427050.02</v>
       </c>
       <c r="N703" t="n">
-        <v>4742883</v>
+        <v>69497864.40000001</v>
       </c>
     </row>
     <row r="704">
@@ -39718,22 +39758,22 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>DIFFERENCIAL ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -39759,13 +39799,13 @@
         <v>1</v>
       </c>
       <c r="L704" t="n">
-        <v>3965005.14</v>
+        <v>33864867.02</v>
       </c>
       <c r="M704" t="n">
-        <v>3965005.14</v>
+        <v>33864867.02</v>
       </c>
       <c r="N704" t="n">
-        <v>2961858.83</v>
+        <v>27896726.26</v>
       </c>
     </row>
     <row r="705">
@@ -39774,50 +39814,50 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9498666</t>
         </is>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F705" t="n">
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I705" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K705" t="n">
         <v>1</v>
       </c>
       <c r="L705" t="n">
-        <v>151298828.22</v>
+        <v>32765091.84</v>
       </c>
       <c r="M705" t="n">
-        <v>151298828.22</v>
+        <v>32765091.84</v>
       </c>
       <c r="N705" t="n">
-        <v>120800000</v>
+        <v>23052682.68</v>
       </c>
     </row>
     <row r="706">
@@ -39826,54 +39866,54 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F706" t="n">
         <v>1</v>
       </c>
       <c r="G706" t="n">
-        <v>115827</v>
+        <v>10774</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I706" t="n">
-        <v>3973</v>
+        <v>5106</v>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K706" t="n">
         <v>1</v>
       </c>
       <c r="L706" t="n">
-        <v>48044257.29</v>
+        <v>6323844.01</v>
       </c>
       <c r="M706" t="n">
-        <v>48044257.29</v>
+        <v>6323844.01</v>
       </c>
       <c r="N706" t="n">
-        <v>36033198.22</v>
+        <v>4742883</v>
       </c>
     </row>
     <row r="707">
@@ -39882,54 +39922,54 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2301617 000004/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>9502187</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F707" t="n">
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>23167</v>
+        <v>1740</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I707" t="n">
-        <v>3999</v>
+        <v>5107</v>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K707" t="n">
         <v>1</v>
       </c>
       <c r="L707" t="n">
-        <v>1904028.2</v>
+        <v>3965005.14</v>
       </c>
       <c r="M707" t="n">
-        <v>1904028.2</v>
+        <v>3965005.14</v>
       </c>
       <c r="N707" t="n">
-        <v>1768342.65</v>
+        <v>2961858.83</v>
       </c>
     </row>
     <row r="708">
@@ -39938,33 +39978,33 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F708" t="n">
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I708" t="n">
@@ -39979,13 +40019,13 @@
         <v>1</v>
       </c>
       <c r="L708" t="n">
-        <v>99982008.22</v>
+        <v>151298828.22</v>
       </c>
       <c r="M708" t="n">
-        <v>99982008.22</v>
+        <v>151298828.22</v>
       </c>
       <c r="N708" t="n">
-        <v>64984305.34</v>
+        <v>120800000</v>
       </c>
     </row>
     <row r="709">
@@ -39994,50 +40034,54 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>9512044</t>
-        </is>
-      </c>
-      <c r="D709" t="inlineStr"/>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
         </is>
       </c>
       <c r="F709" t="n">
         <v>1</v>
       </c>
       <c r="G709" t="n">
-        <v>1872</v>
+        <v>115827</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
         </is>
       </c>
       <c r="I709" t="n">
-        <v>5107</v>
+        <v>3973</v>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K709" t="n">
         <v>1</v>
       </c>
       <c r="L709" t="n">
-        <v>13602005.38</v>
+        <v>48044257.29</v>
       </c>
       <c r="M709" t="n">
-        <v>13602005.38</v>
+        <v>48044257.29</v>
       </c>
       <c r="N709" t="n">
-        <v>11358610.11</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="710">
@@ -40046,50 +40090,54 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>9512043</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr"/>
+          <t>9502187</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F710" t="n">
         <v>1</v>
       </c>
       <c r="G710" t="n">
-        <v>1872</v>
+        <v>23167</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I710" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K710" t="n">
         <v>1</v>
       </c>
       <c r="L710" t="n">
-        <v>73340224.20999999</v>
+        <v>1904028.2</v>
       </c>
       <c r="M710" t="n">
-        <v>73340224.20999999</v>
+        <v>1904028.2</v>
       </c>
       <c r="N710" t="n">
-        <v>44002130</v>
+        <v>1768342.65</v>
       </c>
     </row>
     <row r="711">
@@ -40098,22 +40146,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITAMARACA LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F711" t="n">
@@ -40139,13 +40187,13 @@
         <v>1</v>
       </c>
       <c r="L711" t="n">
-        <v>11437822.96</v>
+        <v>99982008.22</v>
       </c>
       <c r="M711" t="n">
-        <v>11437822.96</v>
+        <v>99982008.22</v>
       </c>
       <c r="N711" t="n">
-        <v>10619818.83</v>
+        <v>64984305.34</v>
       </c>
     </row>
     <row r="712">
@@ -40154,22 +40202,22 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F712" t="n">
@@ -40195,13 +40243,13 @@
         <v>1</v>
       </c>
       <c r="L712" t="n">
-        <v>19019690.63</v>
+        <v>13602005.38</v>
       </c>
       <c r="M712" t="n">
-        <v>19019690.63</v>
+        <v>13602005.38</v>
       </c>
       <c r="N712" t="n">
-        <v>14264750.82</v>
+        <v>11358610.11</v>
       </c>
     </row>
     <row r="713">
@@ -40210,22 +40258,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -40251,13 +40299,13 @@
         <v>1</v>
       </c>
       <c r="L713" t="n">
-        <v>6305546.68</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="M713" t="n">
-        <v>6305546.68</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="N713" t="n">
-        <v>4557819.64</v>
+        <v>44002130</v>
       </c>
     </row>
     <row r="714">
@@ -40266,54 +40314,54 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>CONSTRUTORA ITAMARACA LTDA</t>
         </is>
       </c>
       <c r="F714" t="n">
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I714" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K714" t="n">
         <v>1</v>
       </c>
       <c r="L714" t="n">
-        <v>8281446.48</v>
+        <v>11437822.96</v>
       </c>
       <c r="M714" t="n">
-        <v>0</v>
+        <v>11437822.96</v>
       </c>
       <c r="N714" t="n">
-        <v>0</v>
+        <v>10619818.83</v>
       </c>
     </row>
     <row r="715">
@@ -40322,54 +40370,54 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F715" t="n">
         <v>1</v>
       </c>
       <c r="G715" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I715" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K715" t="n">
         <v>1</v>
       </c>
       <c r="L715" t="n">
-        <v>8281446.48</v>
+        <v>19019690.63</v>
       </c>
       <c r="M715" t="n">
-        <v>8281446.48</v>
+        <v>19019690.63</v>
       </c>
       <c r="N715" t="n">
-        <v>5342582.88</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="716">
@@ -40378,18 +40426,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>9500304</t>
-        </is>
-      </c>
-      <c r="D716" t="inlineStr"/>
+          <t>9493202</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>DM-9493202/2026</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F716" t="n">
@@ -40415,13 +40467,13 @@
         <v>1</v>
       </c>
       <c r="L716" t="n">
-        <v>16936267.4</v>
+        <v>6305546.68</v>
       </c>
       <c r="M716" t="n">
-        <v>16936267.4</v>
+        <v>6305546.68</v>
       </c>
       <c r="N716" t="n">
-        <v>14124998.39</v>
+        <v>4557819.64</v>
       </c>
     </row>
     <row r="717">
@@ -40430,50 +40482,54 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>9519034</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr"/>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F717" t="n">
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I717" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K717" t="n">
         <v>1</v>
       </c>
       <c r="L717" t="n">
-        <v>64979801.54</v>
+        <v>8281446.48</v>
       </c>
       <c r="M717" t="n">
-        <v>64979801.54</v>
+        <v>0</v>
       </c>
       <c r="N717" t="n">
-        <v>46640000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -40482,54 +40538,54 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F718" t="n">
         <v>1</v>
       </c>
       <c r="G718" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I718" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K718" t="n">
         <v>1</v>
       </c>
       <c r="L718" t="n">
-        <v>28640371.76</v>
+        <v>8281446.48</v>
       </c>
       <c r="M718" t="n">
-        <v>28640371.76</v>
+        <v>8281446.48</v>
       </c>
       <c r="N718" t="n">
-        <v>19798000</v>
+        <v>5342582.88</v>
       </c>
     </row>
     <row r="719">
@@ -40538,211 +40594,229 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
+          <t>2301762 000027/2025</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>1</v>
+      </c>
+      <c r="G719" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I719" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K719" t="n">
+        <v>1</v>
+      </c>
+      <c r="L719" t="n">
+        <v>16936267.4</v>
+      </c>
+      <c r="M719" t="n">
+        <v>16936267.4</v>
+      </c>
+      <c r="N719" t="n">
+        <v>14124998.39</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>1</v>
+      </c>
+      <c r="G720" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I720" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K720" t="n">
+        <v>1</v>
+      </c>
+      <c r="L720" t="n">
+        <v>64979801.54</v>
+      </c>
+      <c r="M720" t="n">
+        <v>64979801.54</v>
+      </c>
+      <c r="N720" t="n">
+        <v>46640000</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2301762 000030/2025</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>9504058</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>DM-9504058/2026</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>1</v>
+      </c>
+      <c r="G721" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I721" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K721" t="n">
+        <v>1</v>
+      </c>
+      <c r="L721" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="M721" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="N721" t="n">
+        <v>19798000</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
           <t>2301901 000001/2025</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>9493205</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr">
+      <c r="D722" t="inlineStr">
         <is>
           <t>DO-9493205/2026-L4</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr">
+      <c r="E722" t="inlineStr">
         <is>
           <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
-      <c r="F719" t="n">
-        <v>1</v>
-      </c>
-      <c r="G719" t="n">
+      <c r="F722" t="n">
+        <v>1</v>
+      </c>
+      <c r="G722" t="n">
         <v>66419</v>
       </c>
-      <c r="H719" t="inlineStr">
+      <c r="H722" t="inlineStr">
         <is>
           <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
-      <c r="I719" t="n">
+      <c r="I722" t="n">
         <v>3971</v>
       </c>
-      <c r="J719" t="inlineStr">
+      <c r="J722" t="inlineStr">
         <is>
           <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
-      <c r="K719" t="n">
-        <v>1</v>
-      </c>
-      <c r="L719" t="n">
+      <c r="K722" t="n">
+        <v>1</v>
+      </c>
+      <c r="L722" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="M719" t="n">
+      <c r="M722" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="N719" t="n">
+      <c r="N722" t="n">
         <v>31699998.96</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr"/>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>2301520 000001/2020</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D720" t="inlineStr"/>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="F720" t="n">
-        <v>1</v>
-      </c>
-      <c r="G720" t="n">
-        <v>1740</v>
-      </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
-        </is>
-      </c>
-      <c r="I720" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J720" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K720" t="n">
-        <v>1</v>
-      </c>
-      <c r="L720" t="n">
-        <v>4668587.23</v>
-      </c>
-      <c r="M720" t="n">
-        <v>0</v>
-      </c>
-      <c r="N720" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr"/>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>2301520 000001/2021</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr">
-        <is>
-          <t>IPE ENGENHARIA LTDA</t>
-        </is>
-      </c>
-      <c r="F721" t="n">
-        <v>1</v>
-      </c>
-      <c r="G721" t="n">
-        <v>1740</v>
-      </c>
-      <c r="H721" t="inlineStr">
-        <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
-        </is>
-      </c>
-      <c r="I721" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J721" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K721" t="n">
-        <v>1</v>
-      </c>
-      <c r="L721" t="n">
-        <v>16217686.32</v>
-      </c>
-      <c r="M721" t="n">
-        <v>16217686.32</v>
-      </c>
-      <c r="N721" t="n">
-        <v>12796116.03</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr"/>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>2301520 000005/2026</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="F722" t="n">
-        <v>1</v>
-      </c>
-      <c r="G722" t="n">
-        <v>1740</v>
-      </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
-        </is>
-      </c>
-      <c r="I722" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K722" t="n">
-        <v>2</v>
-      </c>
-      <c r="L722" t="n">
-        <v>18465630.31</v>
-      </c>
-      <c r="M722" t="n">
-        <v>0</v>
-      </c>
-      <c r="N722" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr"/>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2301520 000006/2020</t>
+          <t>2301520 000001/2020</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -40753,18 +40827,18 @@
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F723" t="n">
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I723" t="n">
@@ -40779,20 +40853,20 @@
         <v>1</v>
       </c>
       <c r="L723" t="n">
-        <v>46371045.53</v>
+        <v>4668587.23</v>
       </c>
       <c r="M723" t="n">
-        <v>46371045.53</v>
+        <v>0</v>
       </c>
       <c r="N723" t="n">
-        <v>34303736.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr"/>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2301520 000013/2021</t>
+          <t>2301520 000001/2021</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -40803,7 +40877,7 @@
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F724" t="n">
@@ -40829,20 +40903,20 @@
         <v>1</v>
       </c>
       <c r="L724" t="n">
-        <v>2022624.54</v>
+        <v>16217686.32</v>
       </c>
       <c r="M724" t="n">
-        <v>2022624.54</v>
+        <v>16217686.32</v>
       </c>
       <c r="N724" t="n">
-        <v>1704806.45</v>
+        <v>12796116.03</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr"/>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -40853,46 +40927,46 @@
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F725" t="n">
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>108600</v>
+        <v>1740</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I725" t="n">
-        <v>3964</v>
+        <v>5107</v>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K725" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L725" t="n">
-        <v>540000</v>
+        <v>18465630.31</v>
       </c>
       <c r="M725" t="n">
-        <v>540000</v>
+        <v>0</v>
       </c>
       <c r="N725" t="n">
-        <v>540000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr"/>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000006/2020</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -40903,46 +40977,46 @@
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F726" t="n">
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>108600</v>
+        <v>1872</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I726" t="n">
-        <v>3964</v>
+        <v>5107</v>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K726" t="n">
         <v>1</v>
       </c>
       <c r="L726" t="n">
-        <v>454999.67</v>
+        <v>46371045.53</v>
       </c>
       <c r="M726" t="n">
-        <v>454999.67</v>
+        <v>46371045.53</v>
       </c>
       <c r="N726" t="n">
-        <v>454999.67</v>
+        <v>34303736.06</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr"/>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000013/2021</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -40953,39 +41027,39 @@
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F727" t="n">
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>108600</v>
+        <v>1740</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I727" t="n">
-        <v>3964</v>
+        <v>5107</v>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K727" t="n">
         <v>1</v>
       </c>
       <c r="L727" t="n">
-        <v>508997.33</v>
+        <v>2022624.54</v>
       </c>
       <c r="M727" t="n">
-        <v>508997.33</v>
+        <v>2022624.54</v>
       </c>
       <c r="N727" t="n">
-        <v>508997.33</v>
+        <v>1704806.45</v>
       </c>
     </row>
     <row r="728">
@@ -41003,7 +41077,7 @@
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -41029,13 +41103,13 @@
         <v>1</v>
       </c>
       <c r="L728" t="n">
-        <v>386990</v>
+        <v>540000</v>
       </c>
       <c r="M728" t="n">
-        <v>386990</v>
+        <v>540000</v>
       </c>
       <c r="N728" t="n">
-        <v>386990</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="729">
@@ -41053,7 +41127,7 @@
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F729" t="n">
@@ -41079,13 +41153,13 @@
         <v>1</v>
       </c>
       <c r="L729" t="n">
-        <v>384900</v>
+        <v>454999.67</v>
       </c>
       <c r="M729" t="n">
-        <v>384900</v>
+        <v>454999.67</v>
       </c>
       <c r="N729" t="n">
-        <v>384900</v>
+        <v>454999.67</v>
       </c>
     </row>
     <row r="730">
@@ -41103,7 +41177,7 @@
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F730" t="n">
@@ -41129,20 +41203,20 @@
         <v>1</v>
       </c>
       <c r="L730" t="n">
-        <v>566000</v>
+        <v>508997.33</v>
       </c>
       <c r="M730" t="n">
-        <v>566000</v>
+        <v>508997.33</v>
       </c>
       <c r="N730" t="n">
-        <v>566000</v>
+        <v>508997.33</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr"/>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -41153,46 +41227,46 @@
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F731" t="n">
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>23159</v>
+        <v>108600</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I731" t="n">
-        <v>3981</v>
+        <v>3964</v>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K731" t="n">
         <v>1</v>
       </c>
       <c r="L731" t="n">
-        <v>1947867.48</v>
+        <v>386990</v>
       </c>
       <c r="M731" t="n">
-        <v>0</v>
+        <v>386990</v>
       </c>
       <c r="N731" t="n">
-        <v>0</v>
+        <v>386990</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr"/>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -41203,46 +41277,46 @@
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F732" t="n">
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>23159</v>
+        <v>108600</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I732" t="n">
-        <v>3981</v>
+        <v>3964</v>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K732" t="n">
         <v>1</v>
       </c>
       <c r="L732" t="n">
-        <v>2235628.88</v>
+        <v>384900</v>
       </c>
       <c r="M732" t="n">
-        <v>0</v>
+        <v>384900</v>
       </c>
       <c r="N732" t="n">
-        <v>0</v>
+        <v>384900</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr"/>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -41253,46 +41327,46 @@
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F733" t="n">
         <v>1</v>
       </c>
       <c r="G733" t="n">
-        <v>23159</v>
+        <v>108600</v>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I733" t="n">
-        <v>3981</v>
+        <v>3964</v>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K733" t="n">
         <v>1</v>
       </c>
       <c r="L733" t="n">
-        <v>2251859.48</v>
+        <v>566000</v>
       </c>
       <c r="M733" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
       <c r="N733" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr"/>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2301762 000005/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -41303,46 +41377,46 @@
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F734" t="n">
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>1872</v>
+        <v>23159</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I734" t="n">
-        <v>5107</v>
+        <v>3981</v>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K734" t="n">
         <v>1</v>
       </c>
       <c r="L734" t="n">
-        <v>10768247.16</v>
+        <v>1947867.48</v>
       </c>
       <c r="M734" t="n">
-        <v>10768247.16</v>
+        <v>0</v>
       </c>
       <c r="N734" t="n">
-        <v>8795462.050000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr"/>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2301762 000016/2017</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -41353,46 +41427,46 @@
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F735" t="n">
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>1872</v>
+        <v>23159</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I735" t="n">
-        <v>5107</v>
+        <v>3981</v>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K735" t="n">
         <v>1</v>
       </c>
       <c r="L735" t="n">
-        <v>24277046.87</v>
+        <v>2235628.88</v>
       </c>
       <c r="M735" t="n">
-        <v>24277046.87</v>
+        <v>0</v>
       </c>
       <c r="N735" t="n">
-        <v>24277046.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr"/>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2301762 000016/2017</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -41403,38 +41477,188 @@
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr">
         <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="F736" t="n">
+        <v>1</v>
+      </c>
+      <c r="G736" t="n">
+        <v>23159</v>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>3981</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+        </is>
+      </c>
+      <c r="K736" t="n">
+        <v>1</v>
+      </c>
+      <c r="L736" t="n">
+        <v>2251859.48</v>
+      </c>
+      <c r="M736" t="n">
+        <v>0</v>
+      </c>
+      <c r="N736" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr"/>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2301762 000005/2023</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+        </is>
+      </c>
+      <c r="F737" t="n">
+        <v>1</v>
+      </c>
+      <c r="G737" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I737" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K737" t="n">
+        <v>1</v>
+      </c>
+      <c r="L737" t="n">
+        <v>10768247.16</v>
+      </c>
+      <c r="M737" t="n">
+        <v>10768247.16</v>
+      </c>
+      <c r="N737" t="n">
+        <v>8795462.050000001</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr"/>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2301762 000016/2017</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>1</v>
+      </c>
+      <c r="G738" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K738" t="n">
+        <v>1</v>
+      </c>
+      <c r="L738" t="n">
+        <v>24277046.87</v>
+      </c>
+      <c r="M738" t="n">
+        <v>24277046.87</v>
+      </c>
+      <c r="N738" t="n">
+        <v>24277046.87</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr"/>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2301762 000016/2017</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr">
+        <is>
           <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
-      <c r="F736" t="n">
-        <v>1</v>
-      </c>
-      <c r="G736" t="n">
+      <c r="F739" t="n">
+        <v>1</v>
+      </c>
+      <c r="G739" t="n">
         <v>1872</v>
       </c>
-      <c r="H736" t="inlineStr">
+      <c r="H739" t="inlineStr">
         <is>
           <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
-      <c r="I736" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J736" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K736" t="n">
-        <v>1</v>
-      </c>
-      <c r="L736" t="n">
+      <c r="I739" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K739" t="n">
+        <v>1</v>
+      </c>
+      <c r="L739" t="n">
         <v>12102613.88</v>
       </c>
-      <c r="M736" t="n">
+      <c r="M739" t="n">
         <v>12102613.88</v>
       </c>
-      <c r="N736" t="n">
+      <c r="N739" t="n">
         <v>12102613.88</v>
       </c>
     </row>
